--- a/whoscored/England4_teams.xlsx
+++ b/whoscored/England4_teams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Subramanya.Ganti\Downloads\Sports\football\whoscored\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623A146C-473B-4392-81DC-B5BD8804D596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8C46D6-946D-4A98-9922-489CE64E8EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="112">
   <si>
     <t>team</t>
   </si>
@@ -357,6 +357,12 @@
   <si>
     <t>RC</t>
   </si>
+  <si>
+    <t>York</t>
+  </si>
+  <si>
+    <t>Rotherham</t>
+  </si>
 </sst>
 </file>
 
@@ -674,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV169"/>
+  <dimension ref="A1:AV193"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.25">
@@ -25346,6 +25352,3510 @@
       </c>
       <c r="AV169">
         <v>8.7898870501205206E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>0</v>
+      </c>
+      <c r="B170" t="s">
+        <v>51</v>
+      </c>
+      <c r="C170">
+        <v>9</v>
+      </c>
+      <c r="D170">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="E170">
+        <v>0.11111111111111099</v>
+      </c>
+      <c r="F170">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G170">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="H170">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="I170">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="J170">
+        <v>1.7777777777777699</v>
+      </c>
+      <c r="K170">
+        <v>810</v>
+      </c>
+      <c r="L170">
+        <v>364</v>
+      </c>
+      <c r="M170">
+        <v>0.56868131868131799</v>
+      </c>
+      <c r="N170">
+        <v>38</v>
+      </c>
+      <c r="O170">
+        <v>13</v>
+      </c>
+      <c r="P170">
+        <v>68</v>
+      </c>
+      <c r="Q170">
+        <v>11</v>
+      </c>
+      <c r="R170">
+        <v>1</v>
+      </c>
+      <c r="S170">
+        <v>291</v>
+      </c>
+      <c r="T170">
+        <v>97</v>
+      </c>
+      <c r="U170">
+        <v>75</v>
+      </c>
+      <c r="V170">
+        <v>172</v>
+      </c>
+      <c r="W170">
+        <v>0.43604651162790697</v>
+      </c>
+      <c r="X170">
+        <v>138</v>
+      </c>
+      <c r="Y170">
+        <v>91</v>
+      </c>
+      <c r="Z170">
+        <v>53</v>
+      </c>
+      <c r="AA170">
+        <v>3870</v>
+      </c>
+      <c r="AB170">
+        <v>0.33589251439539303</v>
+      </c>
+      <c r="AC170">
+        <v>0.84263959390862897</v>
+      </c>
+      <c r="AD170">
+        <v>0.15556882651537701</v>
+      </c>
+      <c r="AE170">
+        <v>109</v>
+      </c>
+      <c r="AF170">
+        <v>168</v>
+      </c>
+      <c r="AG170">
+        <v>98</v>
+      </c>
+      <c r="AH170">
+        <v>24</v>
+      </c>
+      <c r="AI170">
+        <v>23</v>
+      </c>
+      <c r="AJ170">
+        <v>141</v>
+      </c>
+      <c r="AK170">
+        <v>0.27659574468085102</v>
+      </c>
+      <c r="AL170">
+        <v>0.32624113475177302</v>
+      </c>
+      <c r="AM170">
+        <v>162</v>
+      </c>
+      <c r="AN170">
+        <v>0.76543209876543195</v>
+      </c>
+      <c r="AO170" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP170">
+        <v>0.58887562958226702</v>
+      </c>
+      <c r="AQ170">
+        <v>13.8888888888888</v>
+      </c>
+      <c r="AR170">
+        <v>2027</v>
+      </c>
+      <c r="AS170">
+        <v>0.69696969696969702</v>
+      </c>
+      <c r="AT170">
+        <v>90</v>
+      </c>
+      <c r="AU170">
+        <v>0.27955670571328101</v>
+      </c>
+      <c r="AV170">
+        <v>0.30906551650893999</v>
+      </c>
+    </row>
+    <row r="171" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>1</v>
+      </c>
+      <c r="B171" t="s">
+        <v>55</v>
+      </c>
+      <c r="C171">
+        <v>7</v>
+      </c>
+      <c r="D171">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="E171">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="F171">
+        <v>0</v>
+      </c>
+      <c r="G171">
+        <v>2.4285714285714199</v>
+      </c>
+      <c r="H171">
+        <v>1.4285714285714199</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171">
+        <v>2.1428571428571401</v>
+      </c>
+      <c r="K171">
+        <v>630</v>
+      </c>
+      <c r="L171">
+        <v>427</v>
+      </c>
+      <c r="M171">
+        <v>0.54332552693208402</v>
+      </c>
+      <c r="N171">
+        <v>23</v>
+      </c>
+      <c r="O171">
+        <v>9</v>
+      </c>
+      <c r="P171">
+        <v>52</v>
+      </c>
+      <c r="Q171">
+        <v>12</v>
+      </c>
+      <c r="R171">
+        <v>1</v>
+      </c>
+      <c r="S171">
+        <v>242</v>
+      </c>
+      <c r="T171">
+        <v>59</v>
+      </c>
+      <c r="U171">
+        <v>37</v>
+      </c>
+      <c r="V171">
+        <v>96</v>
+      </c>
+      <c r="W171">
+        <v>0.38541666666666602</v>
+      </c>
+      <c r="X171">
+        <v>103</v>
+      </c>
+      <c r="Y171">
+        <v>101</v>
+      </c>
+      <c r="Z171">
+        <v>35</v>
+      </c>
+      <c r="AA171">
+        <v>2210</v>
+      </c>
+      <c r="AB171">
+        <v>0.232558139534883</v>
+      </c>
+      <c r="AC171">
+        <v>0.74502487562189001</v>
+      </c>
+      <c r="AD171">
+        <v>0.37437810945273597</v>
+      </c>
+      <c r="AE171">
+        <v>73</v>
+      </c>
+      <c r="AF171">
+        <v>134</v>
+      </c>
+      <c r="AG171">
+        <v>59</v>
+      </c>
+      <c r="AH171">
+        <v>13</v>
+      </c>
+      <c r="AI171">
+        <v>15</v>
+      </c>
+      <c r="AJ171">
+        <v>110</v>
+      </c>
+      <c r="AK171">
+        <v>0.3</v>
+      </c>
+      <c r="AL171">
+        <v>0.32727272727272699</v>
+      </c>
+      <c r="AM171">
+        <v>137</v>
+      </c>
+      <c r="AN171">
+        <v>0.74452554744525501</v>
+      </c>
+      <c r="AO171" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP171">
+        <v>0.51396402823741505</v>
+      </c>
+      <c r="AQ171">
+        <v>11.5714285714285</v>
+      </c>
+      <c r="AR171">
+        <v>2027</v>
+      </c>
+      <c r="AS171">
+        <v>0.6</v>
+      </c>
+      <c r="AT171">
+        <v>90</v>
+      </c>
+      <c r="AU171">
+        <v>0.25411886821705398</v>
+      </c>
+      <c r="AV171">
+        <v>0.25962398892580202</v>
+      </c>
+    </row>
+    <row r="172" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>2</v>
+      </c>
+      <c r="B172" t="s">
+        <v>58</v>
+      </c>
+      <c r="C172">
+        <v>9</v>
+      </c>
+      <c r="D172">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E172">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="F172">
+        <v>0</v>
+      </c>
+      <c r="G172">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="H172">
+        <v>0.77777777777777701</v>
+      </c>
+      <c r="I172">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="J172">
+        <v>1.6666666666666601</v>
+      </c>
+      <c r="K172">
+        <v>810</v>
+      </c>
+      <c r="L172">
+        <v>391</v>
+      </c>
+      <c r="M172">
+        <v>0.43734015345268501</v>
+      </c>
+      <c r="N172">
+        <v>43</v>
+      </c>
+      <c r="O172">
+        <v>11</v>
+      </c>
+      <c r="P172">
+        <v>50</v>
+      </c>
+      <c r="Q172">
+        <v>16</v>
+      </c>
+      <c r="R172">
+        <v>1</v>
+      </c>
+      <c r="S172">
+        <v>255</v>
+      </c>
+      <c r="T172">
+        <v>71</v>
+      </c>
+      <c r="U172">
+        <v>51</v>
+      </c>
+      <c r="V172">
+        <v>122</v>
+      </c>
+      <c r="W172">
+        <v>0.41803278688524498</v>
+      </c>
+      <c r="X172">
+        <v>121</v>
+      </c>
+      <c r="Y172">
+        <v>121</v>
+      </c>
+      <c r="Z172">
+        <v>99</v>
+      </c>
+      <c r="AA172">
+        <v>3348</v>
+      </c>
+      <c r="AB172">
+        <v>0.33028919330289103</v>
+      </c>
+      <c r="AC172">
+        <v>0.85247120029728696</v>
+      </c>
+      <c r="AD172">
+        <v>0.24414715719063501</v>
+      </c>
+      <c r="AE172">
+        <v>80</v>
+      </c>
+      <c r="AF172">
+        <v>115</v>
+      </c>
+      <c r="AG172">
+        <v>73</v>
+      </c>
+      <c r="AH172">
+        <v>25</v>
+      </c>
+      <c r="AI172">
+        <v>34</v>
+      </c>
+      <c r="AJ172">
+        <v>108</v>
+      </c>
+      <c r="AK172">
+        <v>0.28703703703703698</v>
+      </c>
+      <c r="AL172">
+        <v>0.31481481481481399</v>
+      </c>
+      <c r="AM172">
+        <v>203</v>
+      </c>
+      <c r="AN172">
+        <v>0.68965517241379304</v>
+      </c>
+      <c r="AO172" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP172">
+        <v>0.48821008855430997</v>
+      </c>
+      <c r="AQ172">
+        <v>15.5555555555555</v>
+      </c>
+      <c r="AR172">
+        <v>2027</v>
+      </c>
+      <c r="AS172">
+        <v>0.82926829268292601</v>
+      </c>
+      <c r="AT172">
+        <v>90</v>
+      </c>
+      <c r="AU172">
+        <v>0.271231741591199</v>
+      </c>
+      <c r="AV172">
+        <v>0.21676825840880001</v>
+      </c>
+    </row>
+    <row r="173" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>3</v>
+      </c>
+      <c r="B173" t="s">
+        <v>65</v>
+      </c>
+      <c r="C173">
+        <v>9</v>
+      </c>
+      <c r="D173">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="E173">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="F173">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="G173">
+        <v>1.7777777777777699</v>
+      </c>
+      <c r="H173">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="I173">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="J173">
+        <v>1.6666666666666601</v>
+      </c>
+      <c r="K173">
+        <v>810</v>
+      </c>
+      <c r="L173">
+        <v>406</v>
+      </c>
+      <c r="M173">
+        <v>0.45320197044334898</v>
+      </c>
+      <c r="N173">
+        <v>38</v>
+      </c>
+      <c r="O173">
+        <v>34</v>
+      </c>
+      <c r="P173">
+        <v>82</v>
+      </c>
+      <c r="Q173">
+        <v>19</v>
+      </c>
+      <c r="R173">
+        <v>1</v>
+      </c>
+      <c r="S173">
+        <v>345</v>
+      </c>
+      <c r="T173">
+        <v>72</v>
+      </c>
+      <c r="U173">
+        <v>40</v>
+      </c>
+      <c r="V173">
+        <v>112</v>
+      </c>
+      <c r="W173">
+        <v>0.35714285714285698</v>
+      </c>
+      <c r="X173">
+        <v>86</v>
+      </c>
+      <c r="Y173">
+        <v>105</v>
+      </c>
+      <c r="Z173">
+        <v>64</v>
+      </c>
+      <c r="AA173">
+        <v>3301</v>
+      </c>
+      <c r="AB173">
+        <v>0.312893081761006</v>
+      </c>
+      <c r="AC173">
+        <v>0.80300187617260699</v>
+      </c>
+      <c r="AD173">
+        <v>0.23864915572232601</v>
+      </c>
+      <c r="AE173">
+        <v>51</v>
+      </c>
+      <c r="AF173">
+        <v>148</v>
+      </c>
+      <c r="AG173">
+        <v>68</v>
+      </c>
+      <c r="AH173">
+        <v>18</v>
+      </c>
+      <c r="AI173">
+        <v>29</v>
+      </c>
+      <c r="AJ173">
+        <v>83</v>
+      </c>
+      <c r="AK173">
+        <v>0.39759036144578302</v>
+      </c>
+      <c r="AL173">
+        <v>0.33734939759036098</v>
+      </c>
+      <c r="AM173">
+        <v>185</v>
+      </c>
+      <c r="AN173">
+        <v>0.72432432432432403</v>
+      </c>
+      <c r="AO173" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP173">
+        <v>0.446936772097066</v>
+      </c>
+      <c r="AQ173">
+        <v>16.1111111111111</v>
+      </c>
+      <c r="AR173">
+        <v>2027</v>
+      </c>
+      <c r="AS173">
+        <v>0.67441860465116199</v>
+      </c>
+      <c r="AT173">
+        <v>90</v>
+      </c>
+      <c r="AU173">
+        <v>0.27082706314913801</v>
+      </c>
+      <c r="AV173">
+        <v>0.17591738129530601</v>
+      </c>
+    </row>
+    <row r="174" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>4</v>
+      </c>
+      <c r="B174" t="s">
+        <v>61</v>
+      </c>
+      <c r="C174">
+        <v>9</v>
+      </c>
+      <c r="D174">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
+      <c r="F174">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="G174">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="H174">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>1.6666666666666601</v>
+      </c>
+      <c r="K174">
+        <v>810</v>
+      </c>
+      <c r="L174">
+        <v>484</v>
+      </c>
+      <c r="M174">
+        <v>0.55578512396694202</v>
+      </c>
+      <c r="N174">
+        <v>24</v>
+      </c>
+      <c r="O174">
+        <v>17</v>
+      </c>
+      <c r="P174">
+        <v>74</v>
+      </c>
+      <c r="Q174">
+        <v>20</v>
+      </c>
+      <c r="R174">
+        <v>1</v>
+      </c>
+      <c r="S174">
+        <v>286</v>
+      </c>
+      <c r="T174">
+        <v>74</v>
+      </c>
+      <c r="U174">
+        <v>47</v>
+      </c>
+      <c r="V174">
+        <v>121</v>
+      </c>
+      <c r="W174">
+        <v>0.38842975206611502</v>
+      </c>
+      <c r="X174">
+        <v>78</v>
+      </c>
+      <c r="Y174">
+        <v>115</v>
+      </c>
+      <c r="Z174">
+        <v>73</v>
+      </c>
+      <c r="AA174">
+        <v>2647</v>
+      </c>
+      <c r="AB174">
+        <v>0.34756995581737798</v>
+      </c>
+      <c r="AC174">
+        <v>0.73831300813008105</v>
+      </c>
+      <c r="AD174">
+        <v>0.34502032520325199</v>
+      </c>
+      <c r="AE174">
+        <v>103</v>
+      </c>
+      <c r="AF174">
+        <v>143</v>
+      </c>
+      <c r="AG174">
+        <v>66</v>
+      </c>
+      <c r="AH174">
+        <v>22</v>
+      </c>
+      <c r="AI174">
+        <v>15</v>
+      </c>
+      <c r="AJ174">
+        <v>150</v>
+      </c>
+      <c r="AK174">
+        <v>0.293333333333333</v>
+      </c>
+      <c r="AL174">
+        <v>0.38666666666666599</v>
+      </c>
+      <c r="AM174">
+        <v>189</v>
+      </c>
+      <c r="AN174">
+        <v>0.75132275132275095</v>
+      </c>
+      <c r="AO174" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP174">
+        <v>0.45459562344073501</v>
+      </c>
+      <c r="AQ174">
+        <v>9.7777777777777697</v>
+      </c>
+      <c r="AR174">
+        <v>2027</v>
+      </c>
+      <c r="AS174">
+        <v>0.51724137931034397</v>
+      </c>
+      <c r="AT174">
+        <v>90</v>
+      </c>
+      <c r="AU174">
+        <v>0.255894916806159</v>
+      </c>
+      <c r="AV174">
+        <v>0.19850508319384</v>
+      </c>
+    </row>
+    <row r="175" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>5</v>
+      </c>
+      <c r="B175" t="s">
+        <v>110</v>
+      </c>
+      <c r="C175">
+        <v>8</v>
+      </c>
+      <c r="D175">
+        <v>0.5</v>
+      </c>
+      <c r="E175">
+        <v>0.25</v>
+      </c>
+      <c r="F175">
+        <v>0.25</v>
+      </c>
+      <c r="G175">
+        <v>2</v>
+      </c>
+      <c r="H175">
+        <v>1.25</v>
+      </c>
+      <c r="I175">
+        <v>0.75</v>
+      </c>
+      <c r="J175">
+        <v>1.75</v>
+      </c>
+      <c r="K175">
+        <v>720</v>
+      </c>
+      <c r="L175">
+        <v>233</v>
+      </c>
+      <c r="M175">
+        <v>0.40772532188841198</v>
+      </c>
+      <c r="N175">
+        <v>36</v>
+      </c>
+      <c r="O175">
+        <v>10</v>
+      </c>
+      <c r="P175">
+        <v>41</v>
+      </c>
+      <c r="Q175">
+        <v>10</v>
+      </c>
+      <c r="R175">
+        <v>0</v>
+      </c>
+      <c r="S175">
+        <v>156</v>
+      </c>
+      <c r="T175">
+        <v>54</v>
+      </c>
+      <c r="U175">
+        <v>47</v>
+      </c>
+      <c r="V175">
+        <v>101</v>
+      </c>
+      <c r="W175">
+        <v>0.46534653465346498</v>
+      </c>
+      <c r="X175">
+        <v>95</v>
+      </c>
+      <c r="Y175">
+        <v>67</v>
+      </c>
+      <c r="Z175">
+        <v>58</v>
+      </c>
+      <c r="AA175">
+        <v>4355</v>
+      </c>
+      <c r="AB175">
+        <v>0.36312849162011102</v>
+      </c>
+      <c r="AC175">
+        <v>0.89732844421162905</v>
+      </c>
+      <c r="AD175">
+        <v>0.14064955474070101</v>
+      </c>
+      <c r="AE175">
+        <v>100</v>
+      </c>
+      <c r="AF175">
+        <v>110</v>
+      </c>
+      <c r="AG175">
+        <v>78</v>
+      </c>
+      <c r="AH175">
+        <v>15</v>
+      </c>
+      <c r="AI175">
+        <v>20</v>
+      </c>
+      <c r="AJ175">
+        <v>133</v>
+      </c>
+      <c r="AK175">
+        <v>0.33082706766917203</v>
+      </c>
+      <c r="AL175">
+        <v>0.30827067669172897</v>
+      </c>
+      <c r="AM175">
+        <v>157</v>
+      </c>
+      <c r="AN175">
+        <v>0.70063694267515897</v>
+      </c>
+      <c r="AO175" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP175">
+        <v>0.63249717876280498</v>
+      </c>
+      <c r="AQ175">
+        <v>12.5</v>
+      </c>
+      <c r="AR175">
+        <v>2027</v>
+      </c>
+      <c r="AS175">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="AT175">
+        <v>90</v>
+      </c>
+      <c r="AU175">
+        <v>0.28868342728358098</v>
+      </c>
+      <c r="AV175">
+        <v>0.343541572716418</v>
+      </c>
+    </row>
+    <row r="176" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>6</v>
+      </c>
+      <c r="B176" t="s">
+        <v>60</v>
+      </c>
+      <c r="C176">
+        <v>8</v>
+      </c>
+      <c r="D176">
+        <v>0.375</v>
+      </c>
+      <c r="E176">
+        <v>0.625</v>
+      </c>
+      <c r="F176">
+        <v>0</v>
+      </c>
+      <c r="G176">
+        <v>1.375</v>
+      </c>
+      <c r="H176">
+        <v>0.625</v>
+      </c>
+      <c r="I176">
+        <v>0.75</v>
+      </c>
+      <c r="J176">
+        <v>1.75</v>
+      </c>
+      <c r="K176">
+        <v>720</v>
+      </c>
+      <c r="L176">
+        <v>375</v>
+      </c>
+      <c r="M176">
+        <v>0.53066666666666595</v>
+      </c>
+      <c r="N176">
+        <v>34</v>
+      </c>
+      <c r="O176">
+        <v>15</v>
+      </c>
+      <c r="P176">
+        <v>65</v>
+      </c>
+      <c r="Q176">
+        <v>17</v>
+      </c>
+      <c r="R176">
+        <v>0</v>
+      </c>
+      <c r="S176">
+        <v>262</v>
+      </c>
+      <c r="T176">
+        <v>62</v>
+      </c>
+      <c r="U176">
+        <v>56</v>
+      </c>
+      <c r="V176">
+        <v>118</v>
+      </c>
+      <c r="W176">
+        <v>0.47457627118644002</v>
+      </c>
+      <c r="X176">
+        <v>101</v>
+      </c>
+      <c r="Y176">
+        <v>98</v>
+      </c>
+      <c r="Z176">
+        <v>61</v>
+      </c>
+      <c r="AA176">
+        <v>3636</v>
+      </c>
+      <c r="AB176">
+        <v>0.37708333333333299</v>
+      </c>
+      <c r="AC176">
+        <v>0.848225602027883</v>
+      </c>
+      <c r="AD176">
+        <v>0.15209125475285101</v>
+      </c>
+      <c r="AE176">
+        <v>97</v>
+      </c>
+      <c r="AF176">
+        <v>156</v>
+      </c>
+      <c r="AG176">
+        <v>84</v>
+      </c>
+      <c r="AH176">
+        <v>9</v>
+      </c>
+      <c r="AI176">
+        <v>30</v>
+      </c>
+      <c r="AJ176">
+        <v>117</v>
+      </c>
+      <c r="AK176">
+        <v>0.27350427350427298</v>
+      </c>
+      <c r="AL176">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="AM176">
+        <v>148</v>
+      </c>
+      <c r="AN176">
+        <v>0.72972972972972905</v>
+      </c>
+      <c r="AO176" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP176">
+        <v>0.58121260977814204</v>
+      </c>
+      <c r="AQ176">
+        <v>15.625</v>
+      </c>
+      <c r="AR176">
+        <v>2027</v>
+      </c>
+      <c r="AS176">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="AT176">
+        <v>90</v>
+      </c>
+      <c r="AU176">
+        <v>0.27394547040557599</v>
+      </c>
+      <c r="AV176">
+        <v>0.30701702959442301</v>
+      </c>
+    </row>
+    <row r="177" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>7</v>
+      </c>
+      <c r="B177" t="s">
+        <v>53</v>
+      </c>
+      <c r="C177">
+        <v>9</v>
+      </c>
+      <c r="D177">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="E177">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="F177">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G177">
+        <v>1.6666666666666601</v>
+      </c>
+      <c r="H177">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="I177">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="J177">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="K177">
+        <v>810</v>
+      </c>
+      <c r="L177">
+        <v>341</v>
+      </c>
+      <c r="M177">
+        <v>0.442815249266862</v>
+      </c>
+      <c r="N177">
+        <v>24</v>
+      </c>
+      <c r="O177">
+        <v>11</v>
+      </c>
+      <c r="P177">
+        <v>74</v>
+      </c>
+      <c r="Q177">
+        <v>17</v>
+      </c>
+      <c r="R177">
+        <v>0</v>
+      </c>
+      <c r="S177">
+        <v>179</v>
+      </c>
+      <c r="T177">
+        <v>77</v>
+      </c>
+      <c r="U177">
+        <v>69</v>
+      </c>
+      <c r="V177">
+        <v>146</v>
+      </c>
+      <c r="W177">
+        <v>0.47260273972602701</v>
+      </c>
+      <c r="X177">
+        <v>115</v>
+      </c>
+      <c r="Y177">
+        <v>92</v>
+      </c>
+      <c r="Z177">
+        <v>73</v>
+      </c>
+      <c r="AA177">
+        <v>4402</v>
+      </c>
+      <c r="AB177">
+        <v>0.38714090287277703</v>
+      </c>
+      <c r="AC177">
+        <v>0.86870062653227997</v>
+      </c>
+      <c r="AD177">
+        <v>0.19912830291473699</v>
+      </c>
+      <c r="AE177">
+        <v>122</v>
+      </c>
+      <c r="AF177">
+        <v>159</v>
+      </c>
+      <c r="AG177">
+        <v>79</v>
+      </c>
+      <c r="AH177">
+        <v>19</v>
+      </c>
+      <c r="AI177">
+        <v>21</v>
+      </c>
+      <c r="AJ177">
+        <v>167</v>
+      </c>
+      <c r="AK177">
+        <v>0.359281437125748</v>
+      </c>
+      <c r="AL177">
+        <v>0.245508982035928</v>
+      </c>
+      <c r="AM177">
+        <v>190</v>
+      </c>
+      <c r="AN177">
+        <v>0.71578947368420998</v>
+      </c>
+      <c r="AO177" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP177">
+        <v>0.58400686777018096</v>
+      </c>
+      <c r="AQ177">
+        <v>10.7777777777777</v>
+      </c>
+      <c r="AR177">
+        <v>2027</v>
+      </c>
+      <c r="AS177">
+        <v>0.63636363636363602</v>
+      </c>
+      <c r="AT177">
+        <v>90</v>
+      </c>
+      <c r="AU177">
+        <v>0.28758300687094901</v>
+      </c>
+      <c r="AV177">
+        <v>0.29617254868460602</v>
+      </c>
+    </row>
+    <row r="178" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>8</v>
+      </c>
+      <c r="B178" t="s">
+        <v>54</v>
+      </c>
+      <c r="C178">
+        <v>9</v>
+      </c>
+      <c r="D178">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E178">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="F178">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="G178">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="H178">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="I178">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="J178">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="K178">
+        <v>810</v>
+      </c>
+      <c r="L178">
+        <v>543</v>
+      </c>
+      <c r="M178">
+        <v>0.55248618784530301</v>
+      </c>
+      <c r="N178">
+        <v>16</v>
+      </c>
+      <c r="O178">
+        <v>16</v>
+      </c>
+      <c r="P178">
+        <v>69</v>
+      </c>
+      <c r="Q178">
+        <v>13</v>
+      </c>
+      <c r="R178">
+        <v>0</v>
+      </c>
+      <c r="S178">
+        <v>293</v>
+      </c>
+      <c r="T178">
+        <v>55</v>
+      </c>
+      <c r="U178">
+        <v>53</v>
+      </c>
+      <c r="V178">
+        <v>108</v>
+      </c>
+      <c r="W178">
+        <v>0.49074074074073998</v>
+      </c>
+      <c r="X178">
+        <v>112</v>
+      </c>
+      <c r="Y178">
+        <v>113</v>
+      </c>
+      <c r="Z178">
+        <v>77</v>
+      </c>
+      <c r="AA178">
+        <v>3407</v>
+      </c>
+      <c r="AB178">
+        <v>0.42899850523168898</v>
+      </c>
+      <c r="AC178">
+        <v>0.78195763330898405</v>
+      </c>
+      <c r="AD178">
+        <v>0.244338933528122</v>
+      </c>
+      <c r="AE178">
+        <v>95</v>
+      </c>
+      <c r="AF178">
+        <v>156</v>
+      </c>
+      <c r="AG178">
+        <v>78</v>
+      </c>
+      <c r="AH178">
+        <v>26</v>
+      </c>
+      <c r="AI178">
+        <v>17</v>
+      </c>
+      <c r="AJ178">
+        <v>140</v>
+      </c>
+      <c r="AK178">
+        <v>0.307142857142857</v>
+      </c>
+      <c r="AL178">
+        <v>0.314285714285714</v>
+      </c>
+      <c r="AM178">
+        <v>179</v>
+      </c>
+      <c r="AN178">
+        <v>0.73743016759776503</v>
+      </c>
+      <c r="AO178" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP178">
+        <v>0.55451639953396603</v>
+      </c>
+      <c r="AQ178">
+        <v>9.7777777777777697</v>
+      </c>
+      <c r="AR178">
+        <v>2027</v>
+      </c>
+      <c r="AS178">
+        <v>0.62962962962962898</v>
+      </c>
+      <c r="AT178">
+        <v>90</v>
+      </c>
+      <c r="AU178">
+        <v>0.26605235621857398</v>
+      </c>
+      <c r="AV178">
+        <v>0.288225421559203</v>
+      </c>
+    </row>
+    <row r="179" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>9</v>
+      </c>
+      <c r="B179" t="s">
+        <v>64</v>
+      </c>
+      <c r="C179">
+        <v>9</v>
+      </c>
+      <c r="D179">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E179">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="F179">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="G179">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="H179">
+        <v>1</v>
+      </c>
+      <c r="I179">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="J179">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="K179">
+        <v>810</v>
+      </c>
+      <c r="L179">
+        <v>404</v>
+      </c>
+      <c r="M179">
+        <v>0.52227722772277196</v>
+      </c>
+      <c r="N179">
+        <v>37</v>
+      </c>
+      <c r="O179">
+        <v>18</v>
+      </c>
+      <c r="P179">
+        <v>66</v>
+      </c>
+      <c r="Q179">
+        <v>22</v>
+      </c>
+      <c r="R179">
+        <v>1</v>
+      </c>
+      <c r="S179">
+        <v>274</v>
+      </c>
+      <c r="T179">
+        <v>51</v>
+      </c>
+      <c r="U179">
+        <v>46</v>
+      </c>
+      <c r="V179">
+        <v>97</v>
+      </c>
+      <c r="W179">
+        <v>0.47422680412371099</v>
+      </c>
+      <c r="X179">
+        <v>90</v>
+      </c>
+      <c r="Y179">
+        <v>111</v>
+      </c>
+      <c r="Z179">
+        <v>97</v>
+      </c>
+      <c r="AA179">
+        <v>3109</v>
+      </c>
+      <c r="AB179">
+        <v>0.31881804043545803</v>
+      </c>
+      <c r="AC179">
+        <v>0.81143552311435496</v>
+      </c>
+      <c r="AD179">
+        <v>0.26074614760746101</v>
+      </c>
+      <c r="AE179">
+        <v>69</v>
+      </c>
+      <c r="AF179">
+        <v>155</v>
+      </c>
+      <c r="AG179">
+        <v>84</v>
+      </c>
+      <c r="AH179">
+        <v>18</v>
+      </c>
+      <c r="AI179">
+        <v>22</v>
+      </c>
+      <c r="AJ179">
+        <v>95</v>
+      </c>
+      <c r="AK179">
+        <v>0.336842105263157</v>
+      </c>
+      <c r="AL179">
+        <v>0.221052631578947</v>
+      </c>
+      <c r="AM179">
+        <v>209</v>
+      </c>
+      <c r="AN179">
+        <v>0.75598086124401898</v>
+      </c>
+      <c r="AO179" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP179">
+        <v>0.46750117701112498</v>
+      </c>
+      <c r="AQ179">
+        <v>14.4444444444444</v>
+      </c>
+      <c r="AR179">
+        <v>2027</v>
+      </c>
+      <c r="AS179">
+        <v>0.70967741935483797</v>
+      </c>
+      <c r="AT179">
+        <v>90</v>
+      </c>
+      <c r="AU179">
+        <v>0.26634169575287597</v>
+      </c>
+      <c r="AV179">
+        <v>0.20095830424712299</v>
+      </c>
+    </row>
+    <row r="180" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>10</v>
+      </c>
+      <c r="B180" t="s">
+        <v>87</v>
+      </c>
+      <c r="C180">
+        <v>9</v>
+      </c>
+      <c r="D180">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="E180">
+        <v>0.11111111111111099</v>
+      </c>
+      <c r="F180">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="G180">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="H180">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="I180">
+        <v>-0.11111111111111099</v>
+      </c>
+      <c r="J180">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="K180">
+        <v>810</v>
+      </c>
+      <c r="L180">
+        <v>314</v>
+      </c>
+      <c r="M180">
+        <v>0.47133757961783401</v>
+      </c>
+      <c r="N180">
+        <v>40</v>
+      </c>
+      <c r="O180">
+        <v>11</v>
+      </c>
+      <c r="P180">
+        <v>62</v>
+      </c>
+      <c r="Q180">
+        <v>12</v>
+      </c>
+      <c r="R180">
+        <v>3</v>
+      </c>
+      <c r="S180">
+        <v>316</v>
+      </c>
+      <c r="T180">
+        <v>51</v>
+      </c>
+      <c r="U180">
+        <v>35</v>
+      </c>
+      <c r="V180">
+        <v>86</v>
+      </c>
+      <c r="W180">
+        <v>0.40697674418604601</v>
+      </c>
+      <c r="X180">
+        <v>107</v>
+      </c>
+      <c r="Y180">
+        <v>106</v>
+      </c>
+      <c r="Z180">
+        <v>50</v>
+      </c>
+      <c r="AA180">
+        <v>3725</v>
+      </c>
+      <c r="AB180">
+        <v>0.37413793103448201</v>
+      </c>
+      <c r="AC180">
+        <v>0.87853736089030199</v>
+      </c>
+      <c r="AD180">
+        <v>0.18441971383147801</v>
+      </c>
+      <c r="AE180">
+        <v>57</v>
+      </c>
+      <c r="AF180">
+        <v>137</v>
+      </c>
+      <c r="AG180">
+        <v>83</v>
+      </c>
+      <c r="AH180">
+        <v>18</v>
+      </c>
+      <c r="AI180">
+        <v>25</v>
+      </c>
+      <c r="AJ180">
+        <v>79</v>
+      </c>
+      <c r="AK180">
+        <v>0.329113924050632</v>
+      </c>
+      <c r="AL180">
+        <v>0.278481012658227</v>
+      </c>
+      <c r="AM180">
+        <v>147</v>
+      </c>
+      <c r="AN180">
+        <v>0.70068027210884298</v>
+      </c>
+      <c r="AO180" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP180">
+        <v>0.52424781867937997</v>
+      </c>
+      <c r="AQ180">
+        <v>15.8888888888888</v>
+      </c>
+      <c r="AR180">
+        <v>2027</v>
+      </c>
+      <c r="AS180">
+        <v>0.69444444444444398</v>
+      </c>
+      <c r="AT180">
+        <v>90</v>
+      </c>
+      <c r="AU180">
+        <v>0.27602077394331398</v>
+      </c>
+      <c r="AV180">
+        <v>0.24800144827890699</v>
+      </c>
+    </row>
+    <row r="181" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>11</v>
+      </c>
+      <c r="B181" t="s">
+        <v>68</v>
+      </c>
+      <c r="C181">
+        <v>9</v>
+      </c>
+      <c r="D181">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="E181">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="F181">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="G181">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="H181">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="K181">
+        <v>810</v>
+      </c>
+      <c r="L181">
+        <v>508</v>
+      </c>
+      <c r="M181">
+        <v>0.55118110236220397</v>
+      </c>
+      <c r="N181">
+        <v>34</v>
+      </c>
+      <c r="O181">
+        <v>20</v>
+      </c>
+      <c r="P181">
+        <v>68</v>
+      </c>
+      <c r="Q181">
+        <v>22</v>
+      </c>
+      <c r="R181">
+        <v>1</v>
+      </c>
+      <c r="S181">
+        <v>331</v>
+      </c>
+      <c r="T181">
+        <v>70</v>
+      </c>
+      <c r="U181">
+        <v>53</v>
+      </c>
+      <c r="V181">
+        <v>123</v>
+      </c>
+      <c r="W181">
+        <v>0.430894308943089</v>
+      </c>
+      <c r="X181">
+        <v>109</v>
+      </c>
+      <c r="Y181">
+        <v>104</v>
+      </c>
+      <c r="Z181">
+        <v>80</v>
+      </c>
+      <c r="AA181">
+        <v>3057</v>
+      </c>
+      <c r="AB181">
+        <v>0.37057991513437</v>
+      </c>
+      <c r="AC181">
+        <v>0.794468085106383</v>
+      </c>
+      <c r="AD181">
+        <v>0.30085106382978699</v>
+      </c>
+      <c r="AE181">
+        <v>73</v>
+      </c>
+      <c r="AF181">
+        <v>203</v>
+      </c>
+      <c r="AG181">
+        <v>68</v>
+      </c>
+      <c r="AH181">
+        <v>18</v>
+      </c>
+      <c r="AI181">
+        <v>26</v>
+      </c>
+      <c r="AJ181">
+        <v>103</v>
+      </c>
+      <c r="AK181">
+        <v>0.36893203883495101</v>
+      </c>
+      <c r="AL181">
+        <v>0.25242718446601897</v>
+      </c>
+      <c r="AM181">
+        <v>208</v>
+      </c>
+      <c r="AN181">
+        <v>0.69711538461538403</v>
+      </c>
+      <c r="AO181" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP181">
+        <v>0.47241440240140298</v>
+      </c>
+      <c r="AQ181">
+        <v>13.5555555555555</v>
+      </c>
+      <c r="AR181">
+        <v>2027</v>
+      </c>
+      <c r="AS181">
+        <v>0.68421052631578905</v>
+      </c>
+      <c r="AT181">
+        <v>90</v>
+      </c>
+      <c r="AU181">
+        <v>0.26305059241325301</v>
+      </c>
+      <c r="AV181">
+        <v>0.20916051869785701</v>
+      </c>
+    </row>
+    <row r="182" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>12</v>
+      </c>
+      <c r="B182" t="s">
+        <v>56</v>
+      </c>
+      <c r="C182">
+        <v>9</v>
+      </c>
+      <c r="D182">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E182">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="F182">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="G182">
+        <v>1</v>
+      </c>
+      <c r="H182">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="I182">
+        <v>-0.44444444444444398</v>
+      </c>
+      <c r="J182">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="K182">
+        <v>810</v>
+      </c>
+      <c r="L182">
+        <v>431</v>
+      </c>
+      <c r="M182">
+        <v>0.53364269141531295</v>
+      </c>
+      <c r="N182">
+        <v>47</v>
+      </c>
+      <c r="O182">
+        <v>12</v>
+      </c>
+      <c r="P182">
+        <v>84</v>
+      </c>
+      <c r="Q182">
+        <v>16</v>
+      </c>
+      <c r="R182">
+        <v>2</v>
+      </c>
+      <c r="S182">
+        <v>351</v>
+      </c>
+      <c r="T182">
+        <v>53</v>
+      </c>
+      <c r="U182">
+        <v>42</v>
+      </c>
+      <c r="V182">
+        <v>95</v>
+      </c>
+      <c r="W182">
+        <v>0.442105263157894</v>
+      </c>
+      <c r="X182">
+        <v>58</v>
+      </c>
+      <c r="Y182">
+        <v>93</v>
+      </c>
+      <c r="Z182">
+        <v>97</v>
+      </c>
+      <c r="AA182">
+        <v>2979</v>
+      </c>
+      <c r="AB182">
+        <v>0.36063218390804502</v>
+      </c>
+      <c r="AC182">
+        <v>0.79281646955759899</v>
+      </c>
+      <c r="AD182">
+        <v>0.30486202365308801</v>
+      </c>
+      <c r="AE182">
+        <v>56</v>
+      </c>
+      <c r="AF182">
+        <v>154</v>
+      </c>
+      <c r="AG182">
+        <v>76</v>
+      </c>
+      <c r="AH182">
+        <v>16</v>
+      </c>
+      <c r="AI182">
+        <v>37</v>
+      </c>
+      <c r="AJ182">
+        <v>81</v>
+      </c>
+      <c r="AK182">
+        <v>0.34567901234567899</v>
+      </c>
+      <c r="AL182">
+        <v>0.35802469135802401</v>
+      </c>
+      <c r="AM182">
+        <v>274</v>
+      </c>
+      <c r="AN182">
+        <v>0.68978102189780999</v>
+      </c>
+      <c r="AO182" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP182">
+        <v>0.443757626256298</v>
+      </c>
+      <c r="AQ182">
+        <v>15.6666666666666</v>
+      </c>
+      <c r="AR182">
+        <v>2027</v>
+      </c>
+      <c r="AS182">
+        <v>0.74</v>
+      </c>
+      <c r="AT182">
+        <v>90</v>
+      </c>
+      <c r="AU182">
+        <v>0.26174375148096102</v>
+      </c>
+      <c r="AV182">
+        <v>0.18182291518570501</v>
+      </c>
+    </row>
+    <row r="183" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>13</v>
+      </c>
+      <c r="B183" t="s">
+        <v>66</v>
+      </c>
+      <c r="C183">
+        <v>9</v>
+      </c>
+      <c r="D183">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E183">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="F183">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="G183">
+        <v>1</v>
+      </c>
+      <c r="H183">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="I183">
+        <v>-0.55555555555555503</v>
+      </c>
+      <c r="J183">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="K183">
+        <v>810</v>
+      </c>
+      <c r="L183">
+        <v>517</v>
+      </c>
+      <c r="M183">
+        <v>0.51644100580270702</v>
+      </c>
+      <c r="N183">
+        <v>34</v>
+      </c>
+      <c r="O183">
+        <v>13</v>
+      </c>
+      <c r="P183">
+        <v>62</v>
+      </c>
+      <c r="Q183">
+        <v>28</v>
+      </c>
+      <c r="R183">
+        <v>0</v>
+      </c>
+      <c r="S183">
+        <v>275</v>
+      </c>
+      <c r="T183">
+        <v>66</v>
+      </c>
+      <c r="U183">
+        <v>41</v>
+      </c>
+      <c r="V183">
+        <v>107</v>
+      </c>
+      <c r="W183">
+        <v>0.38317757009345699</v>
+      </c>
+      <c r="X183">
+        <v>102</v>
+      </c>
+      <c r="Y183">
+        <v>134</v>
+      </c>
+      <c r="Z183">
+        <v>80</v>
+      </c>
+      <c r="AA183">
+        <v>2569</v>
+      </c>
+      <c r="AB183">
+        <v>0.27629513343799</v>
+      </c>
+      <c r="AC183">
+        <v>0.75931677018633503</v>
+      </c>
+      <c r="AD183">
+        <v>0.32971014492753598</v>
+      </c>
+      <c r="AE183">
+        <v>86</v>
+      </c>
+      <c r="AF183">
+        <v>140</v>
+      </c>
+      <c r="AG183">
+        <v>74</v>
+      </c>
+      <c r="AH183">
+        <v>18</v>
+      </c>
+      <c r="AI183">
+        <v>16</v>
+      </c>
+      <c r="AJ183">
+        <v>120</v>
+      </c>
+      <c r="AK183">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="AL183">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="AM183">
+        <v>195</v>
+      </c>
+      <c r="AN183">
+        <v>0.76923076923076905</v>
+      </c>
+      <c r="AO183" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP183">
+        <v>0.42165922789459598</v>
+      </c>
+      <c r="AQ183">
+        <v>11.3333333333333</v>
+      </c>
+      <c r="AR183">
+        <v>2027</v>
+      </c>
+      <c r="AS183">
+        <v>0.53333333333333299</v>
+      </c>
+      <c r="AT183">
+        <v>90</v>
+      </c>
+      <c r="AU183">
+        <v>0.25812567428161898</v>
+      </c>
+      <c r="AV183">
+        <v>0.163352103496158</v>
+      </c>
+    </row>
+    <row r="184" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>14</v>
+      </c>
+      <c r="B184" t="s">
+        <v>67</v>
+      </c>
+      <c r="C184">
+        <v>9</v>
+      </c>
+      <c r="D184">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="E184">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="F184">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G184">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="H184">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="K184">
+        <v>810</v>
+      </c>
+      <c r="L184">
+        <v>536</v>
+      </c>
+      <c r="M184">
+        <v>0.49253731343283502</v>
+      </c>
+      <c r="N184">
+        <v>38</v>
+      </c>
+      <c r="O184">
+        <v>23</v>
+      </c>
+      <c r="P184">
+        <v>76</v>
+      </c>
+      <c r="Q184">
+        <v>16</v>
+      </c>
+      <c r="R184">
+        <v>0</v>
+      </c>
+      <c r="S184">
+        <v>312</v>
+      </c>
+      <c r="T184">
+        <v>60</v>
+      </c>
+      <c r="U184">
+        <v>42</v>
+      </c>
+      <c r="V184">
+        <v>102</v>
+      </c>
+      <c r="W184">
+        <v>0.41176470588235198</v>
+      </c>
+      <c r="X184">
+        <v>116</v>
+      </c>
+      <c r="Y184">
+        <v>111</v>
+      </c>
+      <c r="Z184">
+        <v>70</v>
+      </c>
+      <c r="AA184">
+        <v>2211</v>
+      </c>
+      <c r="AB184">
+        <v>0.28463855421686701</v>
+      </c>
+      <c r="AC184">
+        <v>0.70394311570782098</v>
+      </c>
+      <c r="AD184">
+        <v>0.42921784098254601</v>
+      </c>
+      <c r="AE184">
+        <v>54</v>
+      </c>
+      <c r="AF184">
+        <v>136</v>
+      </c>
+      <c r="AG184">
+        <v>52</v>
+      </c>
+      <c r="AH184">
+        <v>20</v>
+      </c>
+      <c r="AI184">
+        <v>25</v>
+      </c>
+      <c r="AJ184">
+        <v>92</v>
+      </c>
+      <c r="AK184">
+        <v>0.35869565217391303</v>
+      </c>
+      <c r="AL184">
+        <v>0.23913043478260801</v>
+      </c>
+      <c r="AM184">
+        <v>232</v>
+      </c>
+      <c r="AN184">
+        <v>0.69827586206896497</v>
+      </c>
+      <c r="AO184" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP184">
+        <v>0.37390534491578598</v>
+      </c>
+      <c r="AQ184">
+        <v>14.2222222222222</v>
+      </c>
+      <c r="AR184">
+        <v>2027</v>
+      </c>
+      <c r="AS184">
+        <v>0.67567567567567499</v>
+      </c>
+      <c r="AT184">
+        <v>90</v>
+      </c>
+      <c r="AU184">
+        <v>0.25095749171813297</v>
+      </c>
+      <c r="AV184">
+        <v>0.122786952726311</v>
+      </c>
+    </row>
+    <row r="185" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>63</v>
+      </c>
+      <c r="C185">
+        <v>9</v>
+      </c>
+      <c r="D185">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="E185">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="F185">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G185">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="H185">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="I185">
+        <v>-0.11111111111111099</v>
+      </c>
+      <c r="J185">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="K185">
+        <v>810</v>
+      </c>
+      <c r="L185">
+        <v>608</v>
+      </c>
+      <c r="M185">
+        <v>0.47368421052631499</v>
+      </c>
+      <c r="N185">
+        <v>33</v>
+      </c>
+      <c r="O185">
+        <v>10</v>
+      </c>
+      <c r="P185">
+        <v>76</v>
+      </c>
+      <c r="Q185">
+        <v>24</v>
+      </c>
+      <c r="R185">
+        <v>1</v>
+      </c>
+      <c r="S185">
+        <v>384</v>
+      </c>
+      <c r="T185">
+        <v>52</v>
+      </c>
+      <c r="U185">
+        <v>46</v>
+      </c>
+      <c r="V185">
+        <v>98</v>
+      </c>
+      <c r="W185">
+        <v>0.46938775510204001</v>
+      </c>
+      <c r="X185">
+        <v>82</v>
+      </c>
+      <c r="Y185">
+        <v>141</v>
+      </c>
+      <c r="Z185">
+        <v>78</v>
+      </c>
+      <c r="AA185">
+        <v>2859</v>
+      </c>
+      <c r="AB185">
+        <v>0.313370473537604</v>
+      </c>
+      <c r="AC185">
+        <v>0.75011676786548298</v>
+      </c>
+      <c r="AD185">
+        <v>0.33535730966837901</v>
+      </c>
+      <c r="AE185">
+        <v>94</v>
+      </c>
+      <c r="AF185">
+        <v>160</v>
+      </c>
+      <c r="AG185">
+        <v>53</v>
+      </c>
+      <c r="AH185">
+        <v>19</v>
+      </c>
+      <c r="AI185">
+        <v>29</v>
+      </c>
+      <c r="AJ185">
+        <v>131</v>
+      </c>
+      <c r="AK185">
+        <v>0.32824427480916002</v>
+      </c>
+      <c r="AL185">
+        <v>0.27480916030534303</v>
+      </c>
+      <c r="AM185">
+        <v>204</v>
+      </c>
+      <c r="AN185">
+        <v>0.69607843137254899</v>
+      </c>
+      <c r="AO185" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP185">
+        <v>0.457396828866866</v>
+      </c>
+      <c r="AQ185">
+        <v>13.7777777777777</v>
+      </c>
+      <c r="AR185">
+        <v>2027</v>
+      </c>
+      <c r="AS185">
+        <v>0.67441860465116199</v>
+      </c>
+      <c r="AT185">
+        <v>90</v>
+      </c>
+      <c r="AU185">
+        <v>0.26227292551329001</v>
+      </c>
+      <c r="AV185">
+        <v>0.19492707448670901</v>
+      </c>
+    </row>
+    <row r="186" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>16</v>
+      </c>
+      <c r="B186" t="s">
+        <v>111</v>
+      </c>
+      <c r="C186">
+        <v>9</v>
+      </c>
+      <c r="D186">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="E186">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="F186">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G186">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="H186">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="I186">
+        <v>-0.11111111111111099</v>
+      </c>
+      <c r="J186">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="K186">
+        <v>810</v>
+      </c>
+      <c r="L186">
+        <v>465</v>
+      </c>
+      <c r="M186">
+        <v>0.43870967741935402</v>
+      </c>
+      <c r="N186">
+        <v>29</v>
+      </c>
+      <c r="O186">
+        <v>20</v>
+      </c>
+      <c r="P186">
+        <v>61</v>
+      </c>
+      <c r="Q186">
+        <v>18</v>
+      </c>
+      <c r="R186">
+        <v>0</v>
+      </c>
+      <c r="S186">
+        <v>283</v>
+      </c>
+      <c r="T186">
+        <v>49</v>
+      </c>
+      <c r="U186">
+        <v>41</v>
+      </c>
+      <c r="V186">
+        <v>90</v>
+      </c>
+      <c r="W186">
+        <v>0.45555555555555499</v>
+      </c>
+      <c r="X186">
+        <v>86</v>
+      </c>
+      <c r="Y186">
+        <v>114</v>
+      </c>
+      <c r="Z186">
+        <v>74</v>
+      </c>
+      <c r="AA186">
+        <v>3449</v>
+      </c>
+      <c r="AB186">
+        <v>0.27707454289732703</v>
+      </c>
+      <c r="AC186">
+        <v>0.80423666910153402</v>
+      </c>
+      <c r="AD186">
+        <v>0.25967859751643502</v>
+      </c>
+      <c r="AE186">
+        <v>84</v>
+      </c>
+      <c r="AF186">
+        <v>150</v>
+      </c>
+      <c r="AG186">
+        <v>77</v>
+      </c>
+      <c r="AH186">
+        <v>7</v>
+      </c>
+      <c r="AI186">
+        <v>20</v>
+      </c>
+      <c r="AJ186">
+        <v>114</v>
+      </c>
+      <c r="AK186">
+        <v>0.30701754385964902</v>
+      </c>
+      <c r="AL186">
+        <v>0.31578947368421001</v>
+      </c>
+      <c r="AM186">
+        <v>172</v>
+      </c>
+      <c r="AN186">
+        <v>0.75</v>
+      </c>
+      <c r="AO186" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP186">
+        <v>0.50712934107524499</v>
+      </c>
+      <c r="AQ186">
+        <v>11</v>
+      </c>
+      <c r="AR186">
+        <v>2027</v>
+      </c>
+      <c r="AS186">
+        <v>0.625</v>
+      </c>
+      <c r="AT186">
+        <v>90</v>
+      </c>
+      <c r="AU186">
+        <v>0.274843954411578</v>
+      </c>
+      <c r="AV186">
+        <v>0.23206715669953201</v>
+      </c>
+    </row>
+    <row r="187" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>17</v>
+      </c>
+      <c r="B187" t="s">
+        <v>62</v>
+      </c>
+      <c r="C187">
+        <v>9</v>
+      </c>
+      <c r="D187">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="E187">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="F187">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G187">
+        <v>1</v>
+      </c>
+      <c r="H187">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="I187">
+        <v>-0.11111111111111099</v>
+      </c>
+      <c r="J187">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="K187">
+        <v>810</v>
+      </c>
+      <c r="L187">
+        <v>432</v>
+      </c>
+      <c r="M187">
+        <v>0.43287037037037002</v>
+      </c>
+      <c r="N187">
+        <v>33</v>
+      </c>
+      <c r="O187">
+        <v>19</v>
+      </c>
+      <c r="P187">
+        <v>63</v>
+      </c>
+      <c r="Q187">
+        <v>22</v>
+      </c>
+      <c r="R187">
+        <v>0</v>
+      </c>
+      <c r="S187">
+        <v>295</v>
+      </c>
+      <c r="T187">
+        <v>69</v>
+      </c>
+      <c r="U187">
+        <v>53</v>
+      </c>
+      <c r="V187">
+        <v>122</v>
+      </c>
+      <c r="W187">
+        <v>0.43442622950819598</v>
+      </c>
+      <c r="X187">
+        <v>106</v>
+      </c>
+      <c r="Y187">
+        <v>117</v>
+      </c>
+      <c r="Z187">
+        <v>64</v>
+      </c>
+      <c r="AA187">
+        <v>3319</v>
+      </c>
+      <c r="AB187">
+        <v>0.319620253164556</v>
+      </c>
+      <c r="AC187">
+        <v>0.81317454410122803</v>
+      </c>
+      <c r="AD187">
+        <v>0.235206550055824</v>
+      </c>
+      <c r="AE187">
+        <v>102</v>
+      </c>
+      <c r="AF187">
+        <v>176</v>
+      </c>
+      <c r="AG187">
+        <v>91</v>
+      </c>
+      <c r="AH187">
+        <v>12</v>
+      </c>
+      <c r="AI187">
+        <v>20</v>
+      </c>
+      <c r="AJ187">
+        <v>133</v>
+      </c>
+      <c r="AK187">
+        <v>0.233082706766917</v>
+      </c>
+      <c r="AL187">
+        <v>0.29323308270676601</v>
+      </c>
+      <c r="AM187">
+        <v>214</v>
+      </c>
+      <c r="AN187">
+        <v>0.71962616822429903</v>
+      </c>
+      <c r="AO187" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP187">
+        <v>0.49887023142597697</v>
+      </c>
+      <c r="AQ187">
+        <v>12.8888888888888</v>
+      </c>
+      <c r="AR187">
+        <v>2027</v>
+      </c>
+      <c r="AS187">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="AT187">
+        <v>90</v>
+      </c>
+      <c r="AU187">
+        <v>0.26993371926575599</v>
+      </c>
+      <c r="AV187">
+        <v>0.228721836289798</v>
+      </c>
+    </row>
+    <row r="188" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>18</v>
+      </c>
+      <c r="B188" t="s">
+        <v>59</v>
+      </c>
+      <c r="C188">
+        <v>8</v>
+      </c>
+      <c r="D188">
+        <v>0.25</v>
+      </c>
+      <c r="E188">
+        <v>0.5</v>
+      </c>
+      <c r="F188">
+        <v>0.25</v>
+      </c>
+      <c r="G188">
+        <v>1.25</v>
+      </c>
+      <c r="H188">
+        <v>1.5</v>
+      </c>
+      <c r="I188">
+        <v>-0.25</v>
+      </c>
+      <c r="J188">
+        <v>1.25</v>
+      </c>
+      <c r="K188">
+        <v>720</v>
+      </c>
+      <c r="L188">
+        <v>358</v>
+      </c>
+      <c r="M188">
+        <v>0.54748603351955305</v>
+      </c>
+      <c r="N188">
+        <v>36</v>
+      </c>
+      <c r="O188">
+        <v>14</v>
+      </c>
+      <c r="P188">
+        <v>43</v>
+      </c>
+      <c r="Q188">
+        <v>7</v>
+      </c>
+      <c r="R188">
+        <v>1</v>
+      </c>
+      <c r="S188">
+        <v>299</v>
+      </c>
+      <c r="T188">
+        <v>74</v>
+      </c>
+      <c r="U188">
+        <v>59</v>
+      </c>
+      <c r="V188">
+        <v>133</v>
+      </c>
+      <c r="W188">
+        <v>0.44360902255639001</v>
+      </c>
+      <c r="X188">
+        <v>119</v>
+      </c>
+      <c r="Y188">
+        <v>89</v>
+      </c>
+      <c r="Z188">
+        <v>69</v>
+      </c>
+      <c r="AA188">
+        <v>3318</v>
+      </c>
+      <c r="AB188">
+        <v>0.37408759124087498</v>
+      </c>
+      <c r="AC188">
+        <v>0.85018050541516199</v>
+      </c>
+      <c r="AD188">
+        <v>0.19783393501804999</v>
+      </c>
+      <c r="AE188">
+        <v>78</v>
+      </c>
+      <c r="AF188">
+        <v>164</v>
+      </c>
+      <c r="AG188">
+        <v>79</v>
+      </c>
+      <c r="AH188">
+        <v>16</v>
+      </c>
+      <c r="AI188">
+        <v>25</v>
+      </c>
+      <c r="AJ188">
+        <v>101</v>
+      </c>
+      <c r="AK188">
+        <v>0.32673267326732602</v>
+      </c>
+      <c r="AL188">
+        <v>0.316831683168316</v>
+      </c>
+      <c r="AM188">
+        <v>145</v>
+      </c>
+      <c r="AN188">
+        <v>0.77931034482758599</v>
+      </c>
+      <c r="AO188" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP188">
+        <v>0.53336702066931096</v>
+      </c>
+      <c r="AQ188">
+        <v>14.25</v>
+      </c>
+      <c r="AR188">
+        <v>2027</v>
+      </c>
+      <c r="AS188">
+        <v>0.67567567567567499</v>
+      </c>
+      <c r="AT188">
+        <v>90</v>
+      </c>
+      <c r="AU188">
+        <v>0.26837525703444098</v>
+      </c>
+      <c r="AV188">
+        <v>0.264762242965559</v>
+      </c>
+    </row>
+    <row r="189" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>19</v>
+      </c>
+      <c r="B189" t="s">
+        <v>88</v>
+      </c>
+      <c r="C189">
+        <v>9</v>
+      </c>
+      <c r="D189">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="E189">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="F189">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="G189">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="H189">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="I189">
+        <v>-0.11111111111111099</v>
+      </c>
+      <c r="J189">
+        <v>1</v>
+      </c>
+      <c r="K189">
+        <v>810</v>
+      </c>
+      <c r="L189">
+        <v>577</v>
+      </c>
+      <c r="M189">
+        <v>0.52339688041594401</v>
+      </c>
+      <c r="N189">
+        <v>36</v>
+      </c>
+      <c r="O189">
+        <v>20</v>
+      </c>
+      <c r="P189">
+        <v>63</v>
+      </c>
+      <c r="Q189">
+        <v>15</v>
+      </c>
+      <c r="R189">
+        <v>0</v>
+      </c>
+      <c r="S189">
+        <v>409</v>
+      </c>
+      <c r="T189">
+        <v>60</v>
+      </c>
+      <c r="U189">
+        <v>31</v>
+      </c>
+      <c r="V189">
+        <v>91</v>
+      </c>
+      <c r="W189">
+        <v>0.34065934065934</v>
+      </c>
+      <c r="X189">
+        <v>118</v>
+      </c>
+      <c r="Y189">
+        <v>105</v>
+      </c>
+      <c r="Z189">
+        <v>77</v>
+      </c>
+      <c r="AA189">
+        <v>2797</v>
+      </c>
+      <c r="AB189">
+        <v>0.31490015360983098</v>
+      </c>
+      <c r="AC189">
+        <v>0.78052190121155596</v>
+      </c>
+      <c r="AD189">
+        <v>0.30335507921714799</v>
+      </c>
+      <c r="AE189">
+        <v>72</v>
+      </c>
+      <c r="AF189">
+        <v>157</v>
+      </c>
+      <c r="AG189">
+        <v>66</v>
+      </c>
+      <c r="AH189">
+        <v>19</v>
+      </c>
+      <c r="AI189">
+        <v>25</v>
+      </c>
+      <c r="AJ189">
+        <v>100</v>
+      </c>
+      <c r="AK189">
+        <v>0.32</v>
+      </c>
+      <c r="AL189">
+        <v>0.27</v>
+      </c>
+      <c r="AM189">
+        <v>189</v>
+      </c>
+      <c r="AN189">
+        <v>0.74603174603174605</v>
+      </c>
+      <c r="AO189" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP189">
+        <v>0.44221251691410701</v>
+      </c>
+      <c r="AQ189">
+        <v>12.4444444444444</v>
+      </c>
+      <c r="AR189">
+        <v>2027</v>
+      </c>
+      <c r="AS189">
+        <v>0.80645161290322498</v>
+      </c>
+      <c r="AT189">
+        <v>90</v>
+      </c>
+      <c r="AU189">
+        <v>0.26106699440261799</v>
+      </c>
+      <c r="AV189">
+        <v>0.18095522781960399</v>
+      </c>
+    </row>
+    <row r="190" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>20</v>
+      </c>
+      <c r="B190" t="s">
+        <v>57</v>
+      </c>
+      <c r="C190">
+        <v>8</v>
+      </c>
+      <c r="D190">
+        <v>0.25</v>
+      </c>
+      <c r="E190">
+        <v>0.125</v>
+      </c>
+      <c r="F190">
+        <v>0.625</v>
+      </c>
+      <c r="G190">
+        <v>1.125</v>
+      </c>
+      <c r="H190">
+        <v>1.625</v>
+      </c>
+      <c r="I190">
+        <v>-0.5</v>
+      </c>
+      <c r="J190">
+        <v>0.875</v>
+      </c>
+      <c r="K190">
+        <v>720</v>
+      </c>
+      <c r="L190">
+        <v>373</v>
+      </c>
+      <c r="M190">
+        <v>0.50670241286863205</v>
+      </c>
+      <c r="N190">
+        <v>24</v>
+      </c>
+      <c r="O190">
+        <v>12</v>
+      </c>
+      <c r="P190">
+        <v>47</v>
+      </c>
+      <c r="Q190">
+        <v>11</v>
+      </c>
+      <c r="R190">
+        <v>1</v>
+      </c>
+      <c r="S190">
+        <v>223</v>
+      </c>
+      <c r="T190">
+        <v>55</v>
+      </c>
+      <c r="U190">
+        <v>46</v>
+      </c>
+      <c r="V190">
+        <v>101</v>
+      </c>
+      <c r="W190">
+        <v>0.45544554455445502</v>
+      </c>
+      <c r="X190">
+        <v>97</v>
+      </c>
+      <c r="Y190">
+        <v>102</v>
+      </c>
+      <c r="Z190">
+        <v>64</v>
+      </c>
+      <c r="AA190">
+        <v>2687</v>
+      </c>
+      <c r="AB190">
+        <v>0.35436893203883402</v>
+      </c>
+      <c r="AC190">
+        <v>0.80038666022232896</v>
+      </c>
+      <c r="AD190">
+        <v>0.29869502174963702</v>
+      </c>
+      <c r="AE190">
+        <v>86</v>
+      </c>
+      <c r="AF190">
+        <v>167</v>
+      </c>
+      <c r="AG190">
+        <v>58</v>
+      </c>
+      <c r="AH190">
+        <v>23</v>
+      </c>
+      <c r="AI190">
+        <v>16</v>
+      </c>
+      <c r="AJ190">
+        <v>121</v>
+      </c>
+      <c r="AK190">
+        <v>0.27272727272727199</v>
+      </c>
+      <c r="AL190">
+        <v>0.26446280991735499</v>
+      </c>
+      <c r="AM190">
+        <v>159</v>
+      </c>
+      <c r="AN190">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="AO190" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP190">
+        <v>0.450793987505271</v>
+      </c>
+      <c r="AQ190">
+        <v>11.625</v>
+      </c>
+      <c r="AR190">
+        <v>2027</v>
+      </c>
+      <c r="AS190">
+        <v>0.55172413793103403</v>
+      </c>
+      <c r="AT190">
+        <v>90</v>
+      </c>
+      <c r="AU190">
+        <v>0.25772356160473298</v>
+      </c>
+      <c r="AV190">
+        <v>0.192876438395266</v>
+      </c>
+    </row>
+    <row r="191" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>21</v>
+      </c>
+      <c r="B191" t="s">
+        <v>85</v>
+      </c>
+      <c r="C191">
+        <v>7</v>
+      </c>
+      <c r="D191">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="E191">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="F191">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="G191">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="H191">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="I191">
+        <v>-0.42857142857142799</v>
+      </c>
+      <c r="J191">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="K191">
+        <v>630</v>
+      </c>
+      <c r="L191">
+        <v>333</v>
+      </c>
+      <c r="M191">
+        <v>0.49849849849849798</v>
+      </c>
+      <c r="N191">
+        <v>21</v>
+      </c>
+      <c r="O191">
+        <v>9</v>
+      </c>
+      <c r="P191">
+        <v>56</v>
+      </c>
+      <c r="Q191">
+        <v>11</v>
+      </c>
+      <c r="R191">
+        <v>1</v>
+      </c>
+      <c r="S191">
+        <v>277</v>
+      </c>
+      <c r="T191">
+        <v>66</v>
+      </c>
+      <c r="U191">
+        <v>55</v>
+      </c>
+      <c r="V191">
+        <v>121</v>
+      </c>
+      <c r="W191">
+        <v>0.45454545454545398</v>
+      </c>
+      <c r="X191">
+        <v>76</v>
+      </c>
+      <c r="Y191">
+        <v>79</v>
+      </c>
+      <c r="Z191">
+        <v>72</v>
+      </c>
+      <c r="AA191">
+        <v>2445</v>
+      </c>
+      <c r="AB191">
+        <v>0.244292237442922</v>
+      </c>
+      <c r="AC191">
+        <v>0.82311908320876903</v>
+      </c>
+      <c r="AD191">
+        <v>0.21823617339312401</v>
+      </c>
+      <c r="AE191">
+        <v>50</v>
+      </c>
+      <c r="AF191">
+        <v>146</v>
+      </c>
+      <c r="AG191">
+        <v>60</v>
+      </c>
+      <c r="AH191">
+        <v>12</v>
+      </c>
+      <c r="AI191">
+        <v>16</v>
+      </c>
+      <c r="AJ191">
+        <v>67</v>
+      </c>
+      <c r="AK191">
+        <v>0.35820895522388002</v>
+      </c>
+      <c r="AL191">
+        <v>0.23880597014925301</v>
+      </c>
+      <c r="AM191">
+        <v>145</v>
+      </c>
+      <c r="AN191">
+        <v>0.71724137931034404</v>
+      </c>
+      <c r="AO191" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP191">
+        <v>0.46948774616537198</v>
+      </c>
+      <c r="AQ191">
+        <v>9.8571428571428505</v>
+      </c>
+      <c r="AR191">
+        <v>2027</v>
+      </c>
+      <c r="AS191">
+        <v>0.72727272727272696</v>
+      </c>
+      <c r="AT191">
+        <v>90</v>
+      </c>
+      <c r="AU191">
+        <v>0.25957172942304602</v>
+      </c>
+      <c r="AV191">
+        <v>0.20971398486266701</v>
+      </c>
+    </row>
+    <row r="192" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>22</v>
+      </c>
+      <c r="B192" t="s">
+        <v>73</v>
+      </c>
+      <c r="C192">
+        <v>7</v>
+      </c>
+      <c r="D192">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="E192">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="F192">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="G192">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="H192">
+        <v>1.28571428571428</v>
+      </c>
+      <c r="I192">
+        <v>-0.85714285714285698</v>
+      </c>
+      <c r="J192">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="K192">
+        <v>630</v>
+      </c>
+      <c r="L192">
+        <v>390</v>
+      </c>
+      <c r="M192">
+        <v>0.44615384615384601</v>
+      </c>
+      <c r="N192">
+        <v>24</v>
+      </c>
+      <c r="O192">
+        <v>6</v>
+      </c>
+      <c r="P192">
+        <v>39</v>
+      </c>
+      <c r="Q192">
+        <v>15</v>
+      </c>
+      <c r="R192">
+        <v>0</v>
+      </c>
+      <c r="S192">
+        <v>193</v>
+      </c>
+      <c r="T192">
+        <v>80</v>
+      </c>
+      <c r="U192">
+        <v>43</v>
+      </c>
+      <c r="V192">
+        <v>123</v>
+      </c>
+      <c r="W192">
+        <v>0.34959349593495898</v>
+      </c>
+      <c r="X192">
+        <v>85</v>
+      </c>
+      <c r="Y192">
+        <v>108</v>
+      </c>
+      <c r="Z192">
+        <v>66</v>
+      </c>
+      <c r="AA192">
+        <v>2383</v>
+      </c>
+      <c r="AB192">
+        <v>0.29761904761904701</v>
+      </c>
+      <c r="AC192">
+        <v>0.80255455029270795</v>
+      </c>
+      <c r="AD192">
+        <v>0.26822778073443299</v>
+      </c>
+      <c r="AE192">
+        <v>53</v>
+      </c>
+      <c r="AF192">
+        <v>136</v>
+      </c>
+      <c r="AG192">
+        <v>53</v>
+      </c>
+      <c r="AH192">
+        <v>9</v>
+      </c>
+      <c r="AI192">
+        <v>13</v>
+      </c>
+      <c r="AJ192">
+        <v>76</v>
+      </c>
+      <c r="AK192">
+        <v>0.26315789473684198</v>
+      </c>
+      <c r="AL192">
+        <v>0.23684210526315699</v>
+      </c>
+      <c r="AM192">
+        <v>127</v>
+      </c>
+      <c r="AN192">
+        <v>0.80314960629921195</v>
+      </c>
+      <c r="AO192" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP192">
+        <v>0.50849024416492405</v>
+      </c>
+      <c r="AQ192">
+        <v>11</v>
+      </c>
+      <c r="AR192">
+        <v>2027</v>
+      </c>
+      <c r="AS192">
+        <v>0.59090909090909005</v>
+      </c>
+      <c r="AT192">
+        <v>90</v>
+      </c>
+      <c r="AU192">
+        <v>0.255516998928001</v>
+      </c>
+      <c r="AV192">
+        <v>0.25275442964342698</v>
+      </c>
+    </row>
+    <row r="193" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>23</v>
+      </c>
+      <c r="B193" t="s">
+        <v>69</v>
+      </c>
+      <c r="C193">
+        <v>7</v>
+      </c>
+      <c r="D193">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="E193">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="F193">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="G193">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="H193">
+        <v>1.8571428571428501</v>
+      </c>
+      <c r="I193">
+        <v>-1</v>
+      </c>
+      <c r="J193">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="K193">
+        <v>630</v>
+      </c>
+      <c r="L193">
+        <v>218</v>
+      </c>
+      <c r="M193">
+        <v>0.45871559633027498</v>
+      </c>
+      <c r="N193">
+        <v>30</v>
+      </c>
+      <c r="O193">
+        <v>4</v>
+      </c>
+      <c r="P193">
+        <v>41</v>
+      </c>
+      <c r="Q193">
+        <v>20</v>
+      </c>
+      <c r="R193">
+        <v>2</v>
+      </c>
+      <c r="S193">
+        <v>218</v>
+      </c>
+      <c r="T193">
+        <v>63</v>
+      </c>
+      <c r="U193">
+        <v>73</v>
+      </c>
+      <c r="V193">
+        <v>136</v>
+      </c>
+      <c r="W193">
+        <v>0.53676470588235203</v>
+      </c>
+      <c r="X193">
+        <v>101</v>
+      </c>
+      <c r="Y193">
+        <v>70</v>
+      </c>
+      <c r="Z193">
+        <v>47</v>
+      </c>
+      <c r="AA193">
+        <v>2959</v>
+      </c>
+      <c r="AB193">
+        <v>0.33712984054669698</v>
+      </c>
+      <c r="AC193">
+        <v>0.86746031746031704</v>
+      </c>
+      <c r="AD193">
+        <v>0.174206349206349</v>
+      </c>
+      <c r="AE193">
+        <v>72</v>
+      </c>
+      <c r="AF193">
+        <v>126</v>
+      </c>
+      <c r="AG193">
+        <v>73</v>
+      </c>
+      <c r="AH193">
+        <v>7</v>
+      </c>
+      <c r="AI193">
+        <v>19</v>
+      </c>
+      <c r="AJ193">
+        <v>97</v>
+      </c>
+      <c r="AK193">
+        <v>0.247422680412371</v>
+      </c>
+      <c r="AL193">
+        <v>0.31958762886597902</v>
+      </c>
+      <c r="AM193">
+        <v>137</v>
+      </c>
+      <c r="AN193">
+        <v>0.72992700729926996</v>
+      </c>
+      <c r="AO193" t="s">
+        <v>48</v>
+      </c>
+      <c r="AP193">
+        <v>0.58395128829744003</v>
+      </c>
+      <c r="AQ193">
+        <v>14.285714285714199</v>
+      </c>
+      <c r="AR193">
+        <v>2027</v>
+      </c>
+      <c r="AS193">
+        <v>0.59375</v>
+      </c>
+      <c r="AT193">
+        <v>90</v>
+      </c>
+      <c r="AU193">
+        <v>0.26438753210037202</v>
+      </c>
+      <c r="AV193">
+        <v>0.31931246789962697</v>
       </c>
     </row>
   </sheetData>
@@ -25355,7 +28865,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A23766FC-8705-4FA5-A0D0-6E5FCF7FC6A2}">
-  <dimension ref="A1:AM169"/>
+  <dimension ref="A1:AM193"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.25">
@@ -45464,6 +48974,2862 @@
       </c>
       <c r="AM169">
         <v>0.72067039106145203</v>
+      </c>
+    </row>
+    <row r="170" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>0</v>
+      </c>
+      <c r="B170" t="s">
+        <v>48</v>
+      </c>
+      <c r="C170" t="s">
+        <v>51</v>
+      </c>
+      <c r="D170">
+        <v>2027</v>
+      </c>
+      <c r="E170">
+        <v>9</v>
+      </c>
+      <c r="F170">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="G170">
+        <v>0.11111111111111099</v>
+      </c>
+      <c r="H170">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="I170">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="J170">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="K170">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="L170">
+        <v>1.7777777777777699</v>
+      </c>
+      <c r="M170">
+        <v>90</v>
+      </c>
+      <c r="N170">
+        <v>730.20512040043195</v>
+      </c>
+      <c r="O170">
+        <v>0.58887562958226702</v>
+      </c>
+      <c r="P170">
+        <v>0.33589251439539303</v>
+      </c>
+      <c r="Q170">
+        <v>0.84263959390862897</v>
+      </c>
+      <c r="R170">
+        <v>0.15556882651537701</v>
+      </c>
+      <c r="S170">
+        <v>3.6434108527131699E-2</v>
+      </c>
+      <c r="T170">
+        <v>0.27659574468085102</v>
+      </c>
+      <c r="U170">
+        <v>0.32624113475177302</v>
+      </c>
+      <c r="V170">
+        <v>2.8165374677002499E-2</v>
+      </c>
+      <c r="W170">
+        <v>6.8733850129198901E-2</v>
+      </c>
+      <c r="X170">
+        <v>4.4444444444444398E-2</v>
+      </c>
+      <c r="Y170">
+        <v>0.43604651162790697</v>
+      </c>
+      <c r="Z170">
+        <v>3.5658914728682101E-2</v>
+      </c>
+      <c r="AA170">
+        <v>3.36806750585208E-2</v>
+      </c>
+      <c r="AB170">
+        <v>5.9959003950333802E-2</v>
+      </c>
+      <c r="AC170">
+        <v>0.76543209876543195</v>
+      </c>
+      <c r="AD170">
+        <v>1.96162173417758E-2</v>
+      </c>
+      <c r="AE170">
+        <v>4.4043959691911799E-2</v>
+      </c>
+      <c r="AF170">
+        <v>7.5193798449612395E-2</v>
+      </c>
+      <c r="AG170">
+        <v>8.8828154000494507E-3</v>
+      </c>
+      <c r="AH170">
+        <v>0.134722700234083</v>
+      </c>
+      <c r="AI170">
+        <v>0.56868131868131799</v>
+      </c>
+      <c r="AJ170">
+        <v>5.1405181713249102E-3</v>
+      </c>
+      <c r="AK170">
+        <v>4.0712903916893303E-3</v>
+      </c>
+      <c r="AL170">
+        <v>3.7011730833539399E-4</v>
+      </c>
+      <c r="AM170">
+        <v>0.69696969696969702</v>
+      </c>
+    </row>
+    <row r="171" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>1</v>
+      </c>
+      <c r="B171" t="s">
+        <v>48</v>
+      </c>
+      <c r="C171" t="s">
+        <v>55</v>
+      </c>
+      <c r="D171">
+        <v>2027</v>
+      </c>
+      <c r="E171">
+        <v>7</v>
+      </c>
+      <c r="F171">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="G171">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>2.4285714285714199</v>
+      </c>
+      <c r="J171">
+        <v>1.4285714285714199</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171">
+        <v>2.1428571428571401</v>
+      </c>
+      <c r="M171">
+        <v>90</v>
+      </c>
+      <c r="N171">
+        <v>614.27311712259996</v>
+      </c>
+      <c r="O171">
+        <v>0.51396402823741505</v>
+      </c>
+      <c r="P171">
+        <v>0.232558139534883</v>
+      </c>
+      <c r="Q171">
+        <v>0.74502487562189001</v>
+      </c>
+      <c r="R171">
+        <v>0.37437810945273597</v>
+      </c>
+      <c r="S171">
+        <v>4.9773755656108497E-2</v>
+      </c>
+      <c r="T171">
+        <v>0.3</v>
+      </c>
+      <c r="U171">
+        <v>0.32727272727272699</v>
+      </c>
+      <c r="V171">
+        <v>3.3031674208144797E-2</v>
+      </c>
+      <c r="W171">
+        <v>8.7330316742081401E-2</v>
+      </c>
+      <c r="X171">
+        <v>4.3438914027149299E-2</v>
+      </c>
+      <c r="Y171">
+        <v>0.38541666666666602</v>
+      </c>
+      <c r="Z171">
+        <v>4.6606334841628898E-2</v>
+      </c>
+      <c r="AA171">
+        <v>4.8327397854925999E-2</v>
+      </c>
+      <c r="AB171">
+        <v>6.5553005011137297E-2</v>
+      </c>
+      <c r="AC171">
+        <v>0.74452554744525501</v>
+      </c>
+      <c r="AD171">
+        <v>1.6747118068538701E-2</v>
+      </c>
+      <c r="AE171">
+        <v>4.0193083364492899E-2</v>
+      </c>
+      <c r="AF171">
+        <v>0.109502262443438</v>
+      </c>
+      <c r="AG171">
+        <v>6.2203581397429503E-3</v>
+      </c>
+      <c r="AH171">
+        <v>0.20431484043617201</v>
+      </c>
+      <c r="AI171">
+        <v>0.54332552693208402</v>
+      </c>
+      <c r="AJ171">
+        <v>5.5368023002107603E-3</v>
+      </c>
+      <c r="AK171">
+        <v>5.7418690520704202E-3</v>
+      </c>
+      <c r="AL171">
+        <v>4.78489087672535E-4</v>
+      </c>
+      <c r="AM171">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>2</v>
+      </c>
+      <c r="B172" t="s">
+        <v>48</v>
+      </c>
+      <c r="C172" t="s">
+        <v>58</v>
+      </c>
+      <c r="D172">
+        <v>2027</v>
+      </c>
+      <c r="E172">
+        <v>9</v>
+      </c>
+      <c r="F172">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G172">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="J172">
+        <v>0.77777777777777701</v>
+      </c>
+      <c r="K172">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="L172">
+        <v>1.6666666666666601</v>
+      </c>
+      <c r="M172">
+        <v>90</v>
+      </c>
+      <c r="N172">
+        <v>761.96704804189403</v>
+      </c>
+      <c r="O172">
+        <v>0.48821008855430997</v>
+      </c>
+      <c r="P172">
+        <v>0.33028919330289103</v>
+      </c>
+      <c r="Q172">
+        <v>0.85247120029728696</v>
+      </c>
+      <c r="R172">
+        <v>0.24414715719063501</v>
+      </c>
+      <c r="S172">
+        <v>3.2258064516128997E-2</v>
+      </c>
+      <c r="T172">
+        <v>0.28703703703703698</v>
+      </c>
+      <c r="U172">
+        <v>0.31481481481481399</v>
+      </c>
+      <c r="V172">
+        <v>2.3894862604540001E-2</v>
+      </c>
+      <c r="W172">
+        <v>5.6152927120669001E-2</v>
+      </c>
+      <c r="X172">
+        <v>3.6439665471923503E-2</v>
+      </c>
+      <c r="Y172">
+        <v>0.41803278688524498</v>
+      </c>
+      <c r="Z172">
+        <v>3.6140979689366699E-2</v>
+      </c>
+      <c r="AA172">
+        <v>3.4475847413138597E-2</v>
+      </c>
+      <c r="AB172">
+        <v>5.7839644833612702E-2</v>
+      </c>
+      <c r="AC172">
+        <v>0.68965517241379304</v>
+      </c>
+      <c r="AD172">
+        <v>2.8207511519840599E-2</v>
+      </c>
+      <c r="AE172">
+        <v>2.9632133313771999E-2</v>
+      </c>
+      <c r="AF172">
+        <v>7.6164874551971296E-2</v>
+      </c>
+      <c r="AG172">
+        <v>7.1231089696567303E-3</v>
+      </c>
+      <c r="AH172">
+        <v>0.111405424285431</v>
+      </c>
+      <c r="AI172">
+        <v>0.43734015345268501</v>
+      </c>
+      <c r="AJ172">
+        <v>4.4321566922308504E-3</v>
+      </c>
+      <c r="AK172">
+        <v>4.5587897405803103E-3</v>
+      </c>
+      <c r="AL172">
+        <v>2.8492435878626902E-4</v>
+      </c>
+      <c r="AM172">
+        <v>0.82926829268292601</v>
+      </c>
+    </row>
+    <row r="173" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>3</v>
+      </c>
+      <c r="B173" t="s">
+        <v>48</v>
+      </c>
+      <c r="C173" t="s">
+        <v>65</v>
+      </c>
+      <c r="D173">
+        <v>2027</v>
+      </c>
+      <c r="E173">
+        <v>9</v>
+      </c>
+      <c r="F173">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="G173">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="H173">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="I173">
+        <v>1.7777777777777699</v>
+      </c>
+      <c r="J173">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="K173">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="L173">
+        <v>1.6666666666666601</v>
+      </c>
+      <c r="M173">
+        <v>90</v>
+      </c>
+      <c r="N173">
+        <v>820.64802154636698</v>
+      </c>
+      <c r="O173">
+        <v>0.446936772097066</v>
+      </c>
+      <c r="P173">
+        <v>0.312893081761006</v>
+      </c>
+      <c r="Q173">
+        <v>0.80300187617260699</v>
+      </c>
+      <c r="R173">
+        <v>0.23864915572232601</v>
+      </c>
+      <c r="S173">
+        <v>2.51438957891548E-2</v>
+      </c>
+      <c r="T173">
+        <v>0.39759036144578302</v>
+      </c>
+      <c r="U173">
+        <v>0.33734939759036098</v>
+      </c>
+      <c r="V173">
+        <v>1.5449863677673399E-2</v>
+      </c>
+      <c r="W173">
+        <v>6.5434716752499206E-2</v>
+      </c>
+      <c r="X173">
+        <v>3.3929112390184701E-2</v>
+      </c>
+      <c r="Y173">
+        <v>0.35714285714285698</v>
+      </c>
+      <c r="Z173">
+        <v>2.60527112996061E-2</v>
+      </c>
+      <c r="AA173">
+        <v>2.5704850288918699E-2</v>
+      </c>
+      <c r="AB173">
+        <v>4.52894981280949E-2</v>
+      </c>
+      <c r="AC173">
+        <v>0.72432432432432403</v>
+      </c>
+      <c r="AD173">
+        <v>1.5667718271340898E-2</v>
+      </c>
+      <c r="AE173">
+        <v>3.7700447090414098E-2</v>
+      </c>
+      <c r="AF173">
+        <v>0.104513783701908</v>
+      </c>
+      <c r="AG173">
+        <v>4.4065457638146396E-3</v>
+      </c>
+      <c r="AH173">
+        <v>9.9392087783819097E-2</v>
+      </c>
+      <c r="AI173">
+        <v>0.45320197044334898</v>
+      </c>
+      <c r="AJ173">
+        <v>3.9441304676118699E-3</v>
+      </c>
+      <c r="AK173">
+        <v>4.6513538618043401E-3</v>
+      </c>
+      <c r="AL173">
+        <v>2.4480809798970202E-4</v>
+      </c>
+      <c r="AM173">
+        <v>0.67441860465116199</v>
+      </c>
+    </row>
+    <row r="174" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>4</v>
+      </c>
+      <c r="B174" t="s">
+        <v>48</v>
+      </c>
+      <c r="C174" t="s">
+        <v>61</v>
+      </c>
+      <c r="D174">
+        <v>2027</v>
+      </c>
+      <c r="E174">
+        <v>9</v>
+      </c>
+      <c r="F174">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="I174">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="J174">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>1.6666666666666601</v>
+      </c>
+      <c r="M174">
+        <v>90</v>
+      </c>
+      <c r="N174">
+        <v>646.97303701484896</v>
+      </c>
+      <c r="O174">
+        <v>0.45459562344073501</v>
+      </c>
+      <c r="P174">
+        <v>0.34756995581737798</v>
+      </c>
+      <c r="Q174">
+        <v>0.73831300813008105</v>
+      </c>
+      <c r="R174">
+        <v>0.34502032520325199</v>
+      </c>
+      <c r="S174">
+        <v>5.6667925953910001E-2</v>
+      </c>
+      <c r="T174">
+        <v>0.293333333333333</v>
+      </c>
+      <c r="U174">
+        <v>0.38666666666666599</v>
+      </c>
+      <c r="V174">
+        <v>3.8911975821684902E-2</v>
+      </c>
+      <c r="W174">
+        <v>7.8957310162448002E-2</v>
+      </c>
+      <c r="X174">
+        <v>4.5712126936154097E-2</v>
+      </c>
+      <c r="Y174">
+        <v>0.38842975206611502</v>
+      </c>
+      <c r="Z174">
+        <v>2.9467321496033198E-2</v>
+      </c>
+      <c r="AA174">
+        <v>3.6211834827607897E-2</v>
+      </c>
+      <c r="AB174">
+        <v>5.9513363325372999E-2</v>
+      </c>
+      <c r="AC174">
+        <v>0.75132275132275095</v>
+      </c>
+      <c r="AD174">
+        <v>2.2986642977525E-2</v>
+      </c>
+      <c r="AE174">
+        <v>3.6211834827607897E-2</v>
+      </c>
+      <c r="AF174">
+        <v>0.108046845485455</v>
+      </c>
+      <c r="AG174">
+        <v>6.9274814452815097E-3</v>
+      </c>
+      <c r="AH174">
+        <v>0.15240459179619301</v>
+      </c>
+      <c r="AI174">
+        <v>0.55578512396694202</v>
+      </c>
+      <c r="AJ174">
+        <v>3.0788806423473398E-3</v>
+      </c>
+      <c r="AK174">
+        <v>6.2977104048013701E-3</v>
+      </c>
+      <c r="AL174">
+        <v>3.1488552024006798E-4</v>
+      </c>
+      <c r="AM174">
+        <v>0.51724137931034397</v>
+      </c>
+    </row>
+    <row r="175" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>5</v>
+      </c>
+      <c r="B175" t="s">
+        <v>48</v>
+      </c>
+      <c r="C175" t="s">
+        <v>110</v>
+      </c>
+      <c r="D175">
+        <v>2027</v>
+      </c>
+      <c r="E175">
+        <v>8</v>
+      </c>
+      <c r="F175">
+        <v>0.5</v>
+      </c>
+      <c r="G175">
+        <v>0.25</v>
+      </c>
+      <c r="H175">
+        <v>0.25</v>
+      </c>
+      <c r="I175">
+        <v>2</v>
+      </c>
+      <c r="J175">
+        <v>1.25</v>
+      </c>
+      <c r="K175">
+        <v>0.75</v>
+      </c>
+      <c r="L175">
+        <v>1.75</v>
+      </c>
+      <c r="M175">
+        <v>90</v>
+      </c>
+      <c r="N175">
+        <v>860.67577576365295</v>
+      </c>
+      <c r="O175">
+        <v>0.63249717876280498</v>
+      </c>
+      <c r="P175">
+        <v>0.36312849162011102</v>
+      </c>
+      <c r="Q175">
+        <v>0.89732844421162905</v>
+      </c>
+      <c r="R175">
+        <v>0.14064955474070101</v>
+      </c>
+      <c r="S175">
+        <v>3.0539609644087199E-2</v>
+      </c>
+      <c r="T175">
+        <v>0.33082706766917203</v>
+      </c>
+      <c r="U175">
+        <v>0.30827067669172897</v>
+      </c>
+      <c r="V175">
+        <v>2.2962112514351301E-2</v>
+      </c>
+      <c r="W175">
+        <v>4.3168771526980398E-2</v>
+      </c>
+      <c r="X175">
+        <v>2.31917336394948E-2</v>
+      </c>
+      <c r="Y175">
+        <v>0.46534653465346498</v>
+      </c>
+      <c r="Z175">
+        <v>2.1814006888633702E-2</v>
+      </c>
+      <c r="AA175">
+        <v>2.6477962249001698E-2</v>
+      </c>
+      <c r="AB175">
+        <v>6.2045374225272801E-2</v>
+      </c>
+      <c r="AC175">
+        <v>0.70063694267515897</v>
+      </c>
+      <c r="AD175">
+        <v>2.2921221051374601E-2</v>
+      </c>
+      <c r="AE175">
+        <v>3.4381831577061997E-2</v>
+      </c>
+      <c r="AF175">
+        <v>3.5820895522387999E-2</v>
+      </c>
+      <c r="AG175">
+        <v>5.9279019960451701E-3</v>
+      </c>
+      <c r="AH175">
+        <v>9.2080077671901697E-2</v>
+      </c>
+      <c r="AI175">
+        <v>0.40772532188841198</v>
+      </c>
+      <c r="AJ175">
+        <v>4.9399183300376402E-3</v>
+      </c>
+      <c r="AK175">
+        <v>3.9519346640301102E-3</v>
+      </c>
+      <c r="AL175">
+        <v>0</v>
+      </c>
+      <c r="AM175">
+        <v>0.66666666666666596</v>
+      </c>
+    </row>
+    <row r="176" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>6</v>
+      </c>
+      <c r="B176" t="s">
+        <v>48</v>
+      </c>
+      <c r="C176" t="s">
+        <v>60</v>
+      </c>
+      <c r="D176">
+        <v>2027</v>
+      </c>
+      <c r="E176">
+        <v>8</v>
+      </c>
+      <c r="F176">
+        <v>0.375</v>
+      </c>
+      <c r="G176">
+        <v>0.625</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+      <c r="I176">
+        <v>1.375</v>
+      </c>
+      <c r="J176">
+        <v>0.625</v>
+      </c>
+      <c r="K176">
+        <v>0.75</v>
+      </c>
+      <c r="L176">
+        <v>1.75</v>
+      </c>
+      <c r="M176">
+        <v>90</v>
+      </c>
+      <c r="N176">
+        <v>781.98578687666304</v>
+      </c>
+      <c r="O176">
+        <v>0.58121260977814204</v>
+      </c>
+      <c r="P176">
+        <v>0.37708333333333299</v>
+      </c>
+      <c r="Q176">
+        <v>0.848225602027883</v>
+      </c>
+      <c r="R176">
+        <v>0.15209125475285101</v>
+      </c>
+      <c r="S176">
+        <v>3.2178217821782103E-2</v>
+      </c>
+      <c r="T176">
+        <v>0.27350427350427298</v>
+      </c>
+      <c r="U176">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="V176">
+        <v>2.6677667766776599E-2</v>
+      </c>
+      <c r="W176">
+        <v>6.6006600660066E-2</v>
+      </c>
+      <c r="X176">
+        <v>3.24532453245324E-2</v>
+      </c>
+      <c r="Y176">
+        <v>0.47457627118644002</v>
+      </c>
+      <c r="Z176">
+        <v>2.77777777777777E-2</v>
+      </c>
+      <c r="AA176">
+        <v>3.7406203538883798E-2</v>
+      </c>
+      <c r="AB176">
+        <v>5.6491001262804201E-2</v>
+      </c>
+      <c r="AC176">
+        <v>0.72972972972972905</v>
+      </c>
+      <c r="AD176">
+        <v>2.3283453223182801E-2</v>
+      </c>
+      <c r="AE176">
+        <v>4.3513338810538302E-2</v>
+      </c>
+      <c r="AF176">
+        <v>7.2057205720572004E-2</v>
+      </c>
+      <c r="AG176">
+        <v>3.4352635903056599E-3</v>
+      </c>
+      <c r="AH176">
+        <v>0.14313598292940199</v>
+      </c>
+      <c r="AI176">
+        <v>0.53066666666666595</v>
+      </c>
+      <c r="AJ176">
+        <v>5.9639992887250996E-3</v>
+      </c>
+      <c r="AK176">
+        <v>6.4888312261329097E-3</v>
+      </c>
+      <c r="AL176">
+        <v>0</v>
+      </c>
+      <c r="AM176">
+        <v>0.85714285714285698</v>
+      </c>
+    </row>
+    <row r="177" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>7</v>
+      </c>
+      <c r="B177" t="s">
+        <v>48</v>
+      </c>
+      <c r="C177" t="s">
+        <v>53</v>
+      </c>
+      <c r="D177">
+        <v>2027</v>
+      </c>
+      <c r="E177">
+        <v>9</v>
+      </c>
+      <c r="F177">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="G177">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="H177">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="I177">
+        <v>1.6666666666666601</v>
+      </c>
+      <c r="J177">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="K177">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="L177">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="M177">
+        <v>90</v>
+      </c>
+      <c r="N177">
+        <v>837.50917686739604</v>
+      </c>
+      <c r="O177">
+        <v>0.58400686777018096</v>
+      </c>
+      <c r="P177">
+        <v>0.38714090287277703</v>
+      </c>
+      <c r="Q177">
+        <v>0.86870062653227997</v>
+      </c>
+      <c r="R177">
+        <v>0.19912830291473699</v>
+      </c>
+      <c r="S177">
+        <v>3.7937301226715098E-2</v>
+      </c>
+      <c r="T177">
+        <v>0.359281437125748</v>
+      </c>
+      <c r="U177">
+        <v>0.245508982035928</v>
+      </c>
+      <c r="V177">
+        <v>2.7714675147660101E-2</v>
+      </c>
+      <c r="W177">
+        <v>5.40663334847796E-2</v>
+      </c>
+      <c r="X177">
+        <v>3.3166742389822798E-2</v>
+      </c>
+      <c r="Y177">
+        <v>0.47260273972602701</v>
+      </c>
+      <c r="Z177">
+        <v>2.6124488868695998E-2</v>
+      </c>
+      <c r="AA177">
+        <v>2.93406399947495E-2</v>
+      </c>
+      <c r="AB177">
+        <v>6.0594799989156498E-2</v>
+      </c>
+      <c r="AC177">
+        <v>0.71578947368420998</v>
+      </c>
+      <c r="AD177">
+        <v>2.32811599958338E-2</v>
+      </c>
+      <c r="AE177">
+        <v>3.4762279993779302E-2</v>
+      </c>
+      <c r="AF177">
+        <v>4.0663334847796398E-2</v>
+      </c>
+      <c r="AG177">
+        <v>6.0594799989156503E-3</v>
+      </c>
+      <c r="AH177">
+        <v>0.10875171998053799</v>
+      </c>
+      <c r="AI177">
+        <v>0.442815249266862</v>
+      </c>
+      <c r="AJ177">
+        <v>3.43724888827379E-3</v>
+      </c>
+      <c r="AK177">
+        <v>5.4216399990297997E-3</v>
+      </c>
+      <c r="AL177">
+        <v>0</v>
+      </c>
+      <c r="AM177">
+        <v>0.63636363636363602</v>
+      </c>
+    </row>
+    <row r="178" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>8</v>
+      </c>
+      <c r="B178" t="s">
+        <v>48</v>
+      </c>
+      <c r="C178" t="s">
+        <v>54</v>
+      </c>
+      <c r="D178">
+        <v>2027</v>
+      </c>
+      <c r="E178">
+        <v>9</v>
+      </c>
+      <c r="F178">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G178">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="H178">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="I178">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="J178">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="K178">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="L178">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="M178">
+        <v>90</v>
+      </c>
+      <c r="N178">
+        <v>682.67693412441201</v>
+      </c>
+      <c r="O178">
+        <v>0.55451639953396603</v>
+      </c>
+      <c r="P178">
+        <v>0.42899850523168898</v>
+      </c>
+      <c r="Q178">
+        <v>0.78195763330898405</v>
+      </c>
+      <c r="R178">
+        <v>0.244338933528122</v>
+      </c>
+      <c r="S178">
+        <v>4.1091869680070399E-2</v>
+      </c>
+      <c r="T178">
+        <v>0.307142857142857</v>
+      </c>
+      <c r="U178">
+        <v>0.314285714285714</v>
+      </c>
+      <c r="V178">
+        <v>2.7883768711476301E-2</v>
+      </c>
+      <c r="W178">
+        <v>6.8682125036689107E-2</v>
+      </c>
+      <c r="X178">
+        <v>3.1699442324625703E-2</v>
+      </c>
+      <c r="Y178">
+        <v>0.49074074074073998</v>
+      </c>
+      <c r="Z178">
+        <v>3.2873495744056298E-2</v>
+      </c>
+      <c r="AA178">
+        <v>4.1284685787759602E-2</v>
+      </c>
+      <c r="AB178">
+        <v>6.5397865097424596E-2</v>
+      </c>
+      <c r="AC178">
+        <v>0.73743016759776503</v>
+      </c>
+      <c r="AD178">
+        <v>2.8132042527942401E-2</v>
+      </c>
+      <c r="AE178">
+        <v>3.6900471367820598E-2</v>
+      </c>
+      <c r="AF178">
+        <v>8.5999412973290196E-2</v>
+      </c>
+      <c r="AG178">
+        <v>9.4991312432013402E-3</v>
+      </c>
+      <c r="AH178">
+        <v>0.19838570250224299</v>
+      </c>
+      <c r="AI178">
+        <v>0.55248618784530301</v>
+      </c>
+      <c r="AJ178">
+        <v>3.5723228606911002E-3</v>
+      </c>
+      <c r="AK178">
+        <v>4.7495656216006701E-3</v>
+      </c>
+      <c r="AL178">
+        <v>0</v>
+      </c>
+      <c r="AM178">
+        <v>0.62962962962962898</v>
+      </c>
+    </row>
+    <row r="179" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>9</v>
+      </c>
+      <c r="B179" t="s">
+        <v>48</v>
+      </c>
+      <c r="C179" t="s">
+        <v>64</v>
+      </c>
+      <c r="D179">
+        <v>2027</v>
+      </c>
+      <c r="E179">
+        <v>9</v>
+      </c>
+      <c r="F179">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G179">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="H179">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="I179">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="J179">
+        <v>1</v>
+      </c>
+      <c r="K179">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="L179">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="M179">
+        <v>90</v>
+      </c>
+      <c r="N179">
+        <v>738.91673739299097</v>
+      </c>
+      <c r="O179">
+        <v>0.46750117701112498</v>
+      </c>
+      <c r="P179">
+        <v>0.31881804043545803</v>
+      </c>
+      <c r="Q179">
+        <v>0.81143552311435496</v>
+      </c>
+      <c r="R179">
+        <v>0.26074614760746101</v>
+      </c>
+      <c r="S179">
+        <v>3.0556449018977101E-2</v>
+      </c>
+      <c r="T179">
+        <v>0.336842105263157</v>
+      </c>
+      <c r="U179">
+        <v>0.221052631578947</v>
+      </c>
+      <c r="V179">
+        <v>2.2193631392730701E-2</v>
+      </c>
+      <c r="W179">
+        <v>7.6873592795110898E-2</v>
+      </c>
+      <c r="X179">
+        <v>3.11997426825345E-2</v>
+      </c>
+      <c r="Y179">
+        <v>0.47422680412371099</v>
+      </c>
+      <c r="Z179">
+        <v>2.8948214860083601E-2</v>
+      </c>
+      <c r="AA179">
+        <v>3.13448584674451E-2</v>
+      </c>
+      <c r="AB179">
+        <v>5.9018697474739097E-2</v>
+      </c>
+      <c r="AC179">
+        <v>0.75598086124401898</v>
+      </c>
+      <c r="AD179">
+        <v>2.7391452894974602E-2</v>
+      </c>
+      <c r="AE179">
+        <v>3.4168719590638399E-2</v>
+      </c>
+      <c r="AF179">
+        <v>8.8131231907365701E-2</v>
+      </c>
+      <c r="AG179">
+        <v>5.0829500217478597E-3</v>
+      </c>
+      <c r="AH179">
+        <v>0.11408398937700701</v>
+      </c>
+      <c r="AI179">
+        <v>0.52227722772277196</v>
+      </c>
+      <c r="AJ179">
+        <v>4.0789105112791499E-3</v>
+      </c>
+      <c r="AK179">
+        <v>6.2124944710251701E-3</v>
+      </c>
+      <c r="AL179">
+        <v>2.8238611231932602E-4</v>
+      </c>
+      <c r="AM179">
+        <v>0.70967741935483797</v>
+      </c>
+    </row>
+    <row r="180" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>10</v>
+      </c>
+      <c r="B180" t="s">
+        <v>48</v>
+      </c>
+      <c r="C180" t="s">
+        <v>87</v>
+      </c>
+      <c r="D180">
+        <v>2027</v>
+      </c>
+      <c r="E180">
+        <v>9</v>
+      </c>
+      <c r="F180">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="G180">
+        <v>0.11111111111111099</v>
+      </c>
+      <c r="H180">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="I180">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="J180">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="K180">
+        <v>-0.11111111111111099</v>
+      </c>
+      <c r="L180">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="M180">
+        <v>90</v>
+      </c>
+      <c r="N180">
+        <v>789.49091277385901</v>
+      </c>
+      <c r="O180">
+        <v>0.52424781867937997</v>
+      </c>
+      <c r="P180">
+        <v>0.37413793103448201</v>
+      </c>
+      <c r="Q180">
+        <v>0.87853736089030199</v>
+      </c>
+      <c r="R180">
+        <v>0.18441971383147801</v>
+      </c>
+      <c r="S180">
+        <v>2.1208053691275101E-2</v>
+      </c>
+      <c r="T180">
+        <v>0.329113924050632</v>
+      </c>
+      <c r="U180">
+        <v>0.278481012658227</v>
+      </c>
+      <c r="V180">
+        <v>1.53020134228187E-2</v>
+      </c>
+      <c r="W180">
+        <v>5.9060402684563702E-2</v>
+      </c>
+      <c r="X180">
+        <v>2.3087248322147601E-2</v>
+      </c>
+      <c r="Y180">
+        <v>0.40697674418604601</v>
+      </c>
+      <c r="Z180">
+        <v>2.87248322147651E-2</v>
+      </c>
+      <c r="AA180">
+        <v>3.1357066865499002E-2</v>
+      </c>
+      <c r="AB180">
+        <v>4.3485743671965602E-2</v>
+      </c>
+      <c r="AC180">
+        <v>0.70068027210884298</v>
+      </c>
+      <c r="AD180">
+        <v>1.47910692761787E-2</v>
+      </c>
+      <c r="AE180">
+        <v>3.3427816564163999E-2</v>
+      </c>
+      <c r="AF180">
+        <v>8.4832214765100597E-2</v>
+      </c>
+      <c r="AG180">
+        <v>5.3247849394243603E-3</v>
+      </c>
+      <c r="AH180">
+        <v>9.2887915054402803E-2</v>
+      </c>
+      <c r="AI180">
+        <v>0.47133757961783401</v>
+      </c>
+      <c r="AJ180">
+        <v>4.7002731255412602E-3</v>
+      </c>
+      <c r="AK180">
+        <v>3.5498566262829102E-3</v>
+      </c>
+      <c r="AL180">
+        <v>8.87464156570727E-4</v>
+      </c>
+      <c r="AM180">
+        <v>0.69444444444444398</v>
+      </c>
+    </row>
+    <row r="181" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>11</v>
+      </c>
+      <c r="B181" t="s">
+        <v>48</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181">
+        <v>2027</v>
+      </c>
+      <c r="E181">
+        <v>9</v>
+      </c>
+      <c r="F181">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="G181">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="H181">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="I181">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="J181">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="M181">
+        <v>90</v>
+      </c>
+      <c r="N181">
+        <v>719.00150575438295</v>
+      </c>
+      <c r="O181">
+        <v>0.47241440240140298</v>
+      </c>
+      <c r="P181">
+        <v>0.37057991513437</v>
+      </c>
+      <c r="Q181">
+        <v>0.794468085106383</v>
+      </c>
+      <c r="R181">
+        <v>0.30085106382978699</v>
+      </c>
+      <c r="S181">
+        <v>3.3693163231926698E-2</v>
+      </c>
+      <c r="T181">
+        <v>0.36893203883495101</v>
+      </c>
+      <c r="U181">
+        <v>0.25242718446601897</v>
+      </c>
+      <c r="V181">
+        <v>2.3879620543016001E-2</v>
+      </c>
+      <c r="W181">
+        <v>8.8649002289826598E-2</v>
+      </c>
+      <c r="X181">
+        <v>4.02355250245338E-2</v>
+      </c>
+      <c r="Y181">
+        <v>0.430894308943089</v>
+      </c>
+      <c r="Z181">
+        <v>3.5655871769708802E-2</v>
+      </c>
+      <c r="AA181">
+        <v>3.0462679313469101E-2</v>
+      </c>
+      <c r="AB181">
+        <v>6.0925358626938299E-2</v>
+      </c>
+      <c r="AC181">
+        <v>0.69711538461538403</v>
+      </c>
+      <c r="AD181">
+        <v>2.34328302411301E-2</v>
+      </c>
+      <c r="AE181">
+        <v>3.5735066117723403E-2</v>
+      </c>
+      <c r="AF181">
+        <v>0.108276087667648</v>
+      </c>
+      <c r="AG181">
+        <v>5.2723868042542799E-3</v>
+      </c>
+      <c r="AH181">
+        <v>0.14879847203117599</v>
+      </c>
+      <c r="AI181">
+        <v>0.55118110236220397</v>
+      </c>
+      <c r="AJ181">
+        <v>3.9705629019692696E-3</v>
+      </c>
+      <c r="AK181">
+        <v>6.4440283163107797E-3</v>
+      </c>
+      <c r="AL181">
+        <v>2.9291037801412598E-4</v>
+      </c>
+      <c r="AM181">
+        <v>0.68421052631578905</v>
+      </c>
+    </row>
+    <row r="182" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>12</v>
+      </c>
+      <c r="B182" t="s">
+        <v>48</v>
+      </c>
+      <c r="C182" t="s">
+        <v>56</v>
+      </c>
+      <c r="D182">
+        <v>2027</v>
+      </c>
+      <c r="E182">
+        <v>9</v>
+      </c>
+      <c r="F182">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G182">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="H182">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="I182">
+        <v>1</v>
+      </c>
+      <c r="J182">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="K182">
+        <v>-0.44444444444444398</v>
+      </c>
+      <c r="L182">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="M182">
+        <v>90</v>
+      </c>
+      <c r="N182">
+        <v>745.90267392683802</v>
+      </c>
+      <c r="O182">
+        <v>0.443757626256298</v>
+      </c>
+      <c r="P182">
+        <v>0.36063218390804502</v>
+      </c>
+      <c r="Q182">
+        <v>0.79281646955759899</v>
+      </c>
+      <c r="R182">
+        <v>0.30486202365308801</v>
+      </c>
+      <c r="S182">
+        <v>2.71903323262839E-2</v>
+      </c>
+      <c r="T182">
+        <v>0.34567901234567899</v>
+      </c>
+      <c r="U182">
+        <v>0.35802469135802401</v>
+      </c>
+      <c r="V182">
+        <v>1.8798254447801199E-2</v>
+      </c>
+      <c r="W182">
+        <v>7.7207116482040899E-2</v>
+      </c>
+      <c r="X182">
+        <v>3.1889895938234297E-2</v>
+      </c>
+      <c r="Y182">
+        <v>0.442105263157894</v>
+      </c>
+      <c r="Z182">
+        <v>1.9469620678079801E-2</v>
+      </c>
+      <c r="AA182">
+        <v>2.49054392335766E-2</v>
+      </c>
+      <c r="AB182">
+        <v>7.3377315591397693E-2</v>
+      </c>
+      <c r="AC182">
+        <v>0.68978102189780999</v>
+      </c>
+      <c r="AD182">
+        <v>2.59766409210422E-2</v>
+      </c>
+      <c r="AE182">
+        <v>3.8295460326897297E-2</v>
+      </c>
+      <c r="AF182">
+        <v>0.11782477341389699</v>
+      </c>
+      <c r="AG182">
+        <v>4.2848067498626402E-3</v>
+      </c>
+      <c r="AH182">
+        <v>0.11542198182442399</v>
+      </c>
+      <c r="AI182">
+        <v>0.53364269141531295</v>
+      </c>
+      <c r="AJ182">
+        <v>4.1955399425738296E-3</v>
+      </c>
+      <c r="AK182">
+        <v>4.2848067498626402E-3</v>
+      </c>
+      <c r="AL182">
+        <v>5.3560084373283003E-4</v>
+      </c>
+      <c r="AM182">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="183" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>13</v>
+      </c>
+      <c r="B183" t="s">
+        <v>48</v>
+      </c>
+      <c r="C183" t="s">
+        <v>66</v>
+      </c>
+      <c r="D183">
+        <v>2027</v>
+      </c>
+      <c r="E183">
+        <v>9</v>
+      </c>
+      <c r="F183">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G183">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="H183">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="J183">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="K183">
+        <v>-0.55555555555555503</v>
+      </c>
+      <c r="L183">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="M183">
+        <v>90</v>
+      </c>
+      <c r="N183">
+        <v>676.95528891827803</v>
+      </c>
+      <c r="O183">
+        <v>0.42165922789459598</v>
+      </c>
+      <c r="P183">
+        <v>0.27629513343799</v>
+      </c>
+      <c r="Q183">
+        <v>0.75931677018633503</v>
+      </c>
+      <c r="R183">
+        <v>0.32971014492753598</v>
+      </c>
+      <c r="S183">
+        <v>4.6710782405605202E-2</v>
+      </c>
+      <c r="T183">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="U183">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="V183">
+        <v>3.3476060724017098E-2</v>
+      </c>
+      <c r="W183">
+        <v>8.3300895289996096E-2</v>
+      </c>
+      <c r="X183">
+        <v>4.1650447644998E-2</v>
+      </c>
+      <c r="Y183">
+        <v>0.38317757009345699</v>
+      </c>
+      <c r="Z183">
+        <v>3.9704165044764497E-2</v>
+      </c>
+      <c r="AA183">
+        <v>3.80293141276805E-2</v>
+      </c>
+      <c r="AB183">
+        <v>5.5341166081326103E-2</v>
+      </c>
+      <c r="AC183">
+        <v>0.76923076923076905</v>
+      </c>
+      <c r="AD183">
+        <v>2.2704068135928599E-2</v>
+      </c>
+      <c r="AE183">
+        <v>3.0934292835202801E-2</v>
+      </c>
+      <c r="AF183">
+        <v>0.107045543012845</v>
+      </c>
+      <c r="AG183">
+        <v>5.1084153305839498E-3</v>
+      </c>
+      <c r="AH183">
+        <v>0.146725040328439</v>
+      </c>
+      <c r="AI183">
+        <v>0.51644100580270702</v>
+      </c>
+      <c r="AJ183">
+        <v>3.21640965258989E-3</v>
+      </c>
+      <c r="AK183">
+        <v>7.9464238475750303E-3</v>
+      </c>
+      <c r="AL183">
+        <v>0</v>
+      </c>
+      <c r="AM183">
+        <v>0.53333333333333299</v>
+      </c>
+    </row>
+    <row r="184" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>14</v>
+      </c>
+      <c r="B184" t="s">
+        <v>48</v>
+      </c>
+      <c r="C184" t="s">
+        <v>67</v>
+      </c>
+      <c r="D184">
+        <v>2027</v>
+      </c>
+      <c r="E184">
+        <v>9</v>
+      </c>
+      <c r="F184">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="G184">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="H184">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="I184">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="J184">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="M184">
+        <v>90</v>
+      </c>
+      <c r="N184">
+        <v>657.02903156411696</v>
+      </c>
+      <c r="O184">
+        <v>0.37390534491578598</v>
+      </c>
+      <c r="P184">
+        <v>0.28463855421686701</v>
+      </c>
+      <c r="Q184">
+        <v>0.70394311570782098</v>
+      </c>
+      <c r="R184">
+        <v>0.42921784098254601</v>
+      </c>
+      <c r="S184">
+        <v>4.1610131162369897E-2</v>
+      </c>
+      <c r="T184">
+        <v>0.35869565217391303</v>
+      </c>
+      <c r="U184">
+        <v>0.23913043478260801</v>
+      </c>
+      <c r="V184">
+        <v>2.4423337856173601E-2</v>
+      </c>
+      <c r="W184">
+        <v>8.5029398462234201E-2</v>
+      </c>
+      <c r="X184">
+        <v>4.6132971506105798E-2</v>
+      </c>
+      <c r="Y184">
+        <v>0.41176470588235198</v>
+      </c>
+      <c r="Z184">
+        <v>5.2464947987336003E-2</v>
+      </c>
+      <c r="AA184">
+        <v>2.99816764628138E-2</v>
+      </c>
+      <c r="AB184">
+        <v>6.2664404859214401E-2</v>
+      </c>
+      <c r="AC184">
+        <v>0.69827586206896497</v>
+      </c>
+      <c r="AD184">
+        <v>1.8907363535107798E-2</v>
+      </c>
+      <c r="AE184">
+        <v>3.7004411490139499E-2</v>
+      </c>
+      <c r="AF184">
+        <v>0.14111261872455899</v>
+      </c>
+      <c r="AG184">
+        <v>5.4021038671736602E-3</v>
+      </c>
+      <c r="AH184">
+        <v>0.144776383640254</v>
+      </c>
+      <c r="AI184">
+        <v>0.49253731343283502</v>
+      </c>
+      <c r="AJ184">
+        <v>3.8414960833234898E-3</v>
+      </c>
+      <c r="AK184">
+        <v>4.3216830937389296E-3</v>
+      </c>
+      <c r="AL184">
+        <v>0</v>
+      </c>
+      <c r="AM184">
+        <v>0.67567567567567499</v>
+      </c>
+    </row>
+    <row r="185" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>48</v>
+      </c>
+      <c r="C185" t="s">
+        <v>63</v>
+      </c>
+      <c r="D185">
+        <v>2027</v>
+      </c>
+      <c r="E185">
+        <v>9</v>
+      </c>
+      <c r="F185">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="G185">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="H185">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="I185">
+        <v>1.44444444444444</v>
+      </c>
+      <c r="J185">
+        <v>1.55555555555555</v>
+      </c>
+      <c r="K185">
+        <v>-0.11111111111111099</v>
+      </c>
+      <c r="L185">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="M185">
+        <v>90</v>
+      </c>
+      <c r="N185">
+        <v>694.50998917862898</v>
+      </c>
+      <c r="O185">
+        <v>0.457396828866866</v>
+      </c>
+      <c r="P185">
+        <v>0.313370473537604</v>
+      </c>
+      <c r="Q185">
+        <v>0.75011676786548298</v>
+      </c>
+      <c r="R185">
+        <v>0.33535730966837901</v>
+      </c>
+      <c r="S185">
+        <v>4.5820216859041599E-2</v>
+      </c>
+      <c r="T185">
+        <v>0.32824427480916002</v>
+      </c>
+      <c r="U185">
+        <v>0.27480916030534303</v>
+      </c>
+      <c r="V185">
+        <v>3.2878628891220701E-2</v>
+      </c>
+      <c r="W185">
+        <v>7.4501573976914995E-2</v>
+      </c>
+      <c r="X185">
+        <v>3.4277719482336398E-2</v>
+      </c>
+      <c r="Y185">
+        <v>0.46938775510204001</v>
+      </c>
+      <c r="Z185">
+        <v>2.8681357117873299E-2</v>
+      </c>
+      <c r="AA185">
+        <v>4.1573422509481602E-2</v>
+      </c>
+      <c r="AB185">
+        <v>6.0148781503079798E-2</v>
+      </c>
+      <c r="AC185">
+        <v>0.69607843137254899</v>
+      </c>
+      <c r="AD185">
+        <v>2.2998063515883401E-2</v>
+      </c>
+      <c r="AE185">
+        <v>3.50867892101299E-2</v>
+      </c>
+      <c r="AF185">
+        <v>0.13431269674711399</v>
+      </c>
+      <c r="AG185">
+        <v>5.6020923948946902E-3</v>
+      </c>
+      <c r="AH185">
+        <v>0.17926695663663</v>
+      </c>
+      <c r="AI185">
+        <v>0.47368421052631499</v>
+      </c>
+      <c r="AJ185">
+        <v>4.0623360056546301E-3</v>
+      </c>
+      <c r="AK185">
+        <v>7.0763272356564504E-3</v>
+      </c>
+      <c r="AL185">
+        <v>2.9484696815235199E-4</v>
+      </c>
+      <c r="AM185">
+        <v>0.67441860465116199</v>
+      </c>
+    </row>
+    <row r="186" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>16</v>
+      </c>
+      <c r="B186" t="s">
+        <v>48</v>
+      </c>
+      <c r="C186" t="s">
+        <v>111</v>
+      </c>
+      <c r="D186">
+        <v>2027</v>
+      </c>
+      <c r="E186">
+        <v>9</v>
+      </c>
+      <c r="F186">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="G186">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="H186">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="I186">
+        <v>1.2222222222222201</v>
+      </c>
+      <c r="J186">
+        <v>1.3333333333333299</v>
+      </c>
+      <c r="K186">
+        <v>-0.11111111111111099</v>
+      </c>
+      <c r="L186">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="M186">
+        <v>90</v>
+      </c>
+      <c r="N186">
+        <v>755.66959192243098</v>
+      </c>
+      <c r="O186">
+        <v>0.50712934107524499</v>
+      </c>
+      <c r="P186">
+        <v>0.27707454289732703</v>
+      </c>
+      <c r="Q186">
+        <v>0.80423666910153402</v>
+      </c>
+      <c r="R186">
+        <v>0.25967859751643502</v>
+      </c>
+      <c r="S186">
+        <v>3.3053058857639803E-2</v>
+      </c>
+      <c r="T186">
+        <v>0.30701754385964902</v>
+      </c>
+      <c r="U186">
+        <v>0.31578947368421001</v>
+      </c>
+      <c r="V186">
+        <v>2.4354885474050399E-2</v>
+      </c>
+      <c r="W186">
+        <v>6.5816178602493405E-2</v>
+      </c>
+      <c r="X186">
+        <v>2.60945201507683E-2</v>
+      </c>
+      <c r="Y186">
+        <v>0.45555555555555499</v>
+      </c>
+      <c r="Z186">
+        <v>2.4934763699623001E-2</v>
+      </c>
+      <c r="AA186">
+        <v>3.4009279423458702E-2</v>
+      </c>
+      <c r="AB186">
+        <v>5.1312246147674503E-2</v>
+      </c>
+      <c r="AC186">
+        <v>0.75</v>
+      </c>
+      <c r="AD186">
+        <v>2.20761989239995E-2</v>
+      </c>
+      <c r="AE186">
+        <v>3.2815971373512803E-2</v>
+      </c>
+      <c r="AF186">
+        <v>8.20527689185271E-2</v>
+      </c>
+      <c r="AG186">
+        <v>2.08828908740536E-3</v>
+      </c>
+      <c r="AH186">
+        <v>0.13872206080621299</v>
+      </c>
+      <c r="AI186">
+        <v>0.43870967741935402</v>
+      </c>
+      <c r="AJ186">
+        <v>3.2815971373512799E-3</v>
+      </c>
+      <c r="AK186">
+        <v>5.3698862247566403E-3</v>
+      </c>
+      <c r="AL186">
+        <v>0</v>
+      </c>
+      <c r="AM186">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="187" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>17</v>
+      </c>
+      <c r="B187" t="s">
+        <v>48</v>
+      </c>
+      <c r="C187" t="s">
+        <v>62</v>
+      </c>
+      <c r="D187">
+        <v>2027</v>
+      </c>
+      <c r="E187">
+        <v>9</v>
+      </c>
+      <c r="F187">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="G187">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="H187">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+      <c r="J187">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="K187">
+        <v>-0.11111111111111099</v>
+      </c>
+      <c r="L187">
+        <v>1.1111111111111101</v>
+      </c>
+      <c r="M187">
+        <v>90</v>
+      </c>
+      <c r="N187">
+        <v>739.225863855733</v>
+      </c>
+      <c r="O187">
+        <v>0.49887023142597697</v>
+      </c>
+      <c r="P187">
+        <v>0.319620253164556</v>
+      </c>
+      <c r="Q187">
+        <v>0.81317454410122803</v>
+      </c>
+      <c r="R187">
+        <v>0.235206550055824</v>
+      </c>
+      <c r="S187">
+        <v>4.0072310937029197E-2</v>
+      </c>
+      <c r="T187">
+        <v>0.233082706766917</v>
+      </c>
+      <c r="U187">
+        <v>0.29323308270676601</v>
+      </c>
+      <c r="V187">
+        <v>3.07321482374209E-2</v>
+      </c>
+      <c r="W187">
+        <v>8.0445917445013504E-2</v>
+      </c>
+      <c r="X187">
+        <v>3.6758059656522998E-2</v>
+      </c>
+      <c r="Y187">
+        <v>0.43442622950819598</v>
+      </c>
+      <c r="Z187">
+        <v>3.19373305212413E-2</v>
+      </c>
+      <c r="AA187">
+        <v>3.5092636427508199E-2</v>
+      </c>
+      <c r="AB187">
+        <v>6.4186531585357004E-2</v>
+      </c>
+      <c r="AC187">
+        <v>0.71962616822429903</v>
+      </c>
+      <c r="AD187">
+        <v>1.9195972062910498E-2</v>
+      </c>
+      <c r="AE187">
+        <v>3.4492762300542303E-2</v>
+      </c>
+      <c r="AF187">
+        <v>8.8882193431756504E-2</v>
+      </c>
+      <c r="AG187">
+        <v>3.59924476179571E-3</v>
+      </c>
+      <c r="AH187">
+        <v>0.129572811424645</v>
+      </c>
+      <c r="AI187">
+        <v>0.43287037037037002</v>
+      </c>
+      <c r="AJ187">
+        <v>3.8658554848916898E-3</v>
+      </c>
+      <c r="AK187">
+        <v>6.5986153966254802E-3</v>
+      </c>
+      <c r="AL187">
+        <v>0</v>
+      </c>
+      <c r="AM187">
+        <v>0.66666666666666596</v>
+      </c>
+    </row>
+    <row r="188" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>18</v>
+      </c>
+      <c r="B188" t="s">
+        <v>48</v>
+      </c>
+      <c r="C188" t="s">
+        <v>59</v>
+      </c>
+      <c r="D188">
+        <v>2027</v>
+      </c>
+      <c r="E188">
+        <v>8</v>
+      </c>
+      <c r="F188">
+        <v>0.25</v>
+      </c>
+      <c r="G188">
+        <v>0.5</v>
+      </c>
+      <c r="H188">
+        <v>0.25</v>
+      </c>
+      <c r="I188">
+        <v>1.25</v>
+      </c>
+      <c r="J188">
+        <v>1.5</v>
+      </c>
+      <c r="K188">
+        <v>-0.25</v>
+      </c>
+      <c r="L188">
+        <v>1.25</v>
+      </c>
+      <c r="M188">
+        <v>90</v>
+      </c>
+      <c r="N188">
+        <v>777.60713341357098</v>
+      </c>
+      <c r="O188">
+        <v>0.53336702066931096</v>
+      </c>
+      <c r="P188">
+        <v>0.37408759124087498</v>
+      </c>
+      <c r="Q188">
+        <v>0.85018050541516199</v>
+      </c>
+      <c r="R188">
+        <v>0.19783393501804999</v>
+      </c>
+      <c r="S188">
+        <v>3.04400241109101E-2</v>
+      </c>
+      <c r="T188">
+        <v>0.32673267326732602</v>
+      </c>
+      <c r="U188">
+        <v>0.316831683168316</v>
+      </c>
+      <c r="V188">
+        <v>2.3508137432187999E-2</v>
+      </c>
+      <c r="W188">
+        <v>7.3236889692585794E-2</v>
+      </c>
+      <c r="X188">
+        <v>4.0084388185653998E-2</v>
+      </c>
+      <c r="Y188">
+        <v>0.44360902255639001</v>
+      </c>
+      <c r="Z188">
+        <v>3.5864978902953502E-2</v>
+      </c>
+      <c r="AA188">
+        <v>3.06594496168279E-2</v>
+      </c>
+      <c r="AB188">
+        <v>4.9950788701573601E-2</v>
+      </c>
+      <c r="AC188">
+        <v>0.77931034482758599</v>
+      </c>
+      <c r="AD188">
+        <v>2.3769685657990199E-2</v>
+      </c>
+      <c r="AE188">
+        <v>3.2037402408595497E-2</v>
+      </c>
+      <c r="AF188">
+        <v>9.0114526823387497E-2</v>
+      </c>
+      <c r="AG188">
+        <v>5.5118111670701903E-3</v>
+      </c>
+      <c r="AH188">
+        <v>0.123326774863195</v>
+      </c>
+      <c r="AI188">
+        <v>0.54748603351955305</v>
+      </c>
+      <c r="AJ188">
+        <v>4.9089568206718897E-3</v>
+      </c>
+      <c r="AK188">
+        <v>2.4114173855932001E-3</v>
+      </c>
+      <c r="AL188">
+        <v>3.44488197941887E-4</v>
+      </c>
+      <c r="AM188">
+        <v>0.67567567567567499</v>
+      </c>
+    </row>
+    <row r="189" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>19</v>
+      </c>
+      <c r="B189" t="s">
+        <v>48</v>
+      </c>
+      <c r="C189" t="s">
+        <v>88</v>
+      </c>
+      <c r="D189">
+        <v>2027</v>
+      </c>
+      <c r="E189">
+        <v>9</v>
+      </c>
+      <c r="F189">
+        <v>0.22222222222222199</v>
+      </c>
+      <c r="G189">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="H189">
+        <v>0.44444444444444398</v>
+      </c>
+      <c r="I189">
+        <v>0.55555555555555503</v>
+      </c>
+      <c r="J189">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="K189">
+        <v>-0.11111111111111099</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
+      </c>
+      <c r="M189">
+        <v>90</v>
+      </c>
+      <c r="N189">
+        <v>702.77924276426904</v>
+      </c>
+      <c r="O189">
+        <v>0.44221251691410701</v>
+      </c>
+      <c r="P189">
+        <v>0.31490015360983098</v>
+      </c>
+      <c r="Q189">
+        <v>0.78052190121155596</v>
+      </c>
+      <c r="R189">
+        <v>0.30335507921714799</v>
+      </c>
+      <c r="S189">
+        <v>3.5752592062924499E-2</v>
+      </c>
+      <c r="T189">
+        <v>0.32</v>
+      </c>
+      <c r="U189">
+        <v>0.27</v>
+      </c>
+      <c r="V189">
+        <v>2.5741866285305601E-2</v>
+      </c>
+      <c r="W189">
+        <v>7.9728280300321697E-2</v>
+      </c>
+      <c r="X189">
+        <v>3.2534858777261297E-2</v>
+      </c>
+      <c r="Y189">
+        <v>0.34065934065934</v>
+      </c>
+      <c r="Z189">
+        <v>4.2188058634250902E-2</v>
+      </c>
+      <c r="AA189">
+        <v>2.97617935358193E-2</v>
+      </c>
+      <c r="AB189">
+        <v>5.3571228364474803E-2</v>
+      </c>
+      <c r="AC189">
+        <v>0.74603174603174605</v>
+      </c>
+      <c r="AD189">
+        <v>2.1825315259600801E-2</v>
+      </c>
+      <c r="AE189">
+        <v>3.3730032673928503E-2</v>
+      </c>
+      <c r="AF189">
+        <v>0.14622810153736099</v>
+      </c>
+      <c r="AG189">
+        <v>5.3854674017196902E-3</v>
+      </c>
+      <c r="AH189">
+        <v>0.16354814162064499</v>
+      </c>
+      <c r="AI189">
+        <v>0.52339688041594401</v>
+      </c>
+      <c r="AJ189">
+        <v>3.5273236783193202E-3</v>
+      </c>
+      <c r="AK189">
+        <v>4.2516847908313296E-3</v>
+      </c>
+      <c r="AL189">
+        <v>0</v>
+      </c>
+      <c r="AM189">
+        <v>0.80645161290322498</v>
+      </c>
+    </row>
+    <row r="190" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>20</v>
+      </c>
+      <c r="B190" t="s">
+        <v>48</v>
+      </c>
+      <c r="C190" t="s">
+        <v>57</v>
+      </c>
+      <c r="D190">
+        <v>2027</v>
+      </c>
+      <c r="E190">
+        <v>8</v>
+      </c>
+      <c r="F190">
+        <v>0.25</v>
+      </c>
+      <c r="G190">
+        <v>0.125</v>
+      </c>
+      <c r="H190">
+        <v>0.625</v>
+      </c>
+      <c r="I190">
+        <v>1.125</v>
+      </c>
+      <c r="J190">
+        <v>1.625</v>
+      </c>
+      <c r="K190">
+        <v>-0.5</v>
+      </c>
+      <c r="L190">
+        <v>0.875</v>
+      </c>
+      <c r="M190">
+        <v>90</v>
+      </c>
+      <c r="N190">
+        <v>745.07426742481198</v>
+      </c>
+      <c r="O190">
+        <v>0.450793987505271</v>
+      </c>
+      <c r="P190">
+        <v>0.35436893203883402</v>
+      </c>
+      <c r="Q190">
+        <v>0.80038666022232896</v>
+      </c>
+      <c r="R190">
+        <v>0.29869502174963702</v>
+      </c>
+      <c r="S190">
+        <v>4.5031633792333402E-2</v>
+      </c>
+      <c r="T190">
+        <v>0.27272727272727199</v>
+      </c>
+      <c r="U190">
+        <v>0.26446280991735499</v>
+      </c>
+      <c r="V190">
+        <v>3.2005954596203902E-2</v>
+      </c>
+      <c r="W190">
+        <v>8.3736509117975394E-2</v>
+      </c>
+      <c r="X190">
+        <v>3.7588388537402297E-2</v>
+      </c>
+      <c r="Y190">
+        <v>0.45544554455445502</v>
+      </c>
+      <c r="Z190">
+        <v>3.6099739486416003E-2</v>
+      </c>
+      <c r="AA190">
+        <v>3.1158413552982999E-2</v>
+      </c>
+      <c r="AB190">
+        <v>4.8570468185532303E-2</v>
+      </c>
+      <c r="AC190">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="AD190">
+        <v>1.9550377131283402E-2</v>
+      </c>
+      <c r="AE190">
+        <v>2.5354395342133199E-2</v>
+      </c>
+      <c r="AF190">
+        <v>8.2992184592482296E-2</v>
+      </c>
+      <c r="AG190">
+        <v>7.0259167815549996E-3</v>
+      </c>
+      <c r="AH190">
+        <v>0.113942041718261</v>
+      </c>
+      <c r="AI190">
+        <v>0.50670241286863205</v>
+      </c>
+      <c r="AJ190">
+        <v>3.5511427211120301E-3</v>
+      </c>
+      <c r="AK190">
+        <v>3.3602210694393402E-3</v>
+      </c>
+      <c r="AL190">
+        <v>3.0547464267630402E-4</v>
+      </c>
+      <c r="AM190">
+        <v>0.55172413793103403</v>
+      </c>
+    </row>
+    <row r="191" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>21</v>
+      </c>
+      <c r="B191" t="s">
+        <v>48</v>
+      </c>
+      <c r="C191" t="s">
+        <v>85</v>
+      </c>
+      <c r="D191">
+        <v>2027</v>
+      </c>
+      <c r="E191">
+        <v>7</v>
+      </c>
+      <c r="F191">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="G191">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="H191">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="I191">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="J191">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="K191">
+        <v>-0.42857142857142799</v>
+      </c>
+      <c r="L191">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="M191">
+        <v>90</v>
+      </c>
+      <c r="N191">
+        <v>743.97195057500403</v>
+      </c>
+      <c r="O191">
+        <v>0.46948774616537198</v>
+      </c>
+      <c r="P191">
+        <v>0.244292237442922</v>
+      </c>
+      <c r="Q191">
+        <v>0.82311908320876903</v>
+      </c>
+      <c r="R191">
+        <v>0.21823617339312401</v>
+      </c>
+      <c r="S191">
+        <v>2.7402862985684999E-2</v>
+      </c>
+      <c r="T191">
+        <v>0.35820895522388002</v>
+      </c>
+      <c r="U191">
+        <v>0.23880597014925301</v>
+      </c>
+      <c r="V191">
+        <v>2.04498977505112E-2</v>
+      </c>
+      <c r="W191">
+        <v>8.4253578732106302E-2</v>
+      </c>
+      <c r="X191">
+        <v>4.9488752556237199E-2</v>
+      </c>
+      <c r="Y191">
+        <v>0.45454545454545398</v>
+      </c>
+      <c r="Z191">
+        <v>3.1083844580776999E-2</v>
+      </c>
+      <c r="AA191">
+        <v>2.8594141999525601E-2</v>
+      </c>
+      <c r="AB191">
+        <v>5.2482918859888802E-2</v>
+      </c>
+      <c r="AC191">
+        <v>0.71724137931034404</v>
+      </c>
+      <c r="AD191">
+        <v>2.6060483847668899E-2</v>
+      </c>
+      <c r="AE191">
+        <v>3.11278001513823E-2</v>
+      </c>
+      <c r="AF191">
+        <v>0.113292433537832</v>
+      </c>
+      <c r="AG191">
+        <v>4.34341397461148E-3</v>
+      </c>
+      <c r="AH191">
+        <v>0.12052973779546799</v>
+      </c>
+      <c r="AI191">
+        <v>0.49849849849849798</v>
+      </c>
+      <c r="AJ191">
+        <v>3.567804336288E-3</v>
+      </c>
+      <c r="AK191">
+        <v>3.9814628100605298E-3</v>
+      </c>
+      <c r="AL191">
+        <v>3.6195116455095701E-4</v>
+      </c>
+      <c r="AM191">
+        <v>0.72727272727272696</v>
+      </c>
+    </row>
+    <row r="192" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>22</v>
+      </c>
+      <c r="B192" t="s">
+        <v>48</v>
+      </c>
+      <c r="C192" t="s">
+        <v>73</v>
+      </c>
+      <c r="D192">
+        <v>2027</v>
+      </c>
+      <c r="E192">
+        <v>7</v>
+      </c>
+      <c r="F192">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="G192">
+        <v>0.28571428571428498</v>
+      </c>
+      <c r="H192">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="I192">
+        <v>0.42857142857142799</v>
+      </c>
+      <c r="J192">
+        <v>1.28571428571428</v>
+      </c>
+      <c r="K192">
+        <v>-0.85714285714285698</v>
+      </c>
+      <c r="L192">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="M192">
+        <v>90</v>
+      </c>
+      <c r="N192">
+        <v>669.48889449717001</v>
+      </c>
+      <c r="O192">
+        <v>0.50849024416492405</v>
+      </c>
+      <c r="P192">
+        <v>0.29761904761904701</v>
+      </c>
+      <c r="Q192">
+        <v>0.80255455029270795</v>
+      </c>
+      <c r="R192">
+        <v>0.26822778073443299</v>
+      </c>
+      <c r="S192">
+        <v>3.1892572387746503E-2</v>
+      </c>
+      <c r="T192">
+        <v>0.26315789473684198</v>
+      </c>
+      <c r="U192">
+        <v>0.23684210526315699</v>
+      </c>
+      <c r="V192">
+        <v>2.2240872849349499E-2</v>
+      </c>
+      <c r="W192">
+        <v>7.9311791859001196E-2</v>
+      </c>
+      <c r="X192">
+        <v>5.1615610574905497E-2</v>
+      </c>
+      <c r="Y192">
+        <v>0.34959349593495898</v>
+      </c>
+      <c r="Z192">
+        <v>3.5669324381032298E-2</v>
+      </c>
+      <c r="AA192">
+        <v>4.6886757068414602E-2</v>
+      </c>
+      <c r="AB192">
+        <v>5.5135353219339399E-2</v>
+      </c>
+      <c r="AC192">
+        <v>0.80314960629921195</v>
+      </c>
+      <c r="AD192">
+        <v>2.86530182084756E-2</v>
+      </c>
+      <c r="AE192">
+        <v>2.9955428127042698E-2</v>
+      </c>
+      <c r="AF192">
+        <v>8.0990348300461604E-2</v>
+      </c>
+      <c r="AG192">
+        <v>3.9072297557012203E-3</v>
+      </c>
+      <c r="AH192">
+        <v>0.16931328941371901</v>
+      </c>
+      <c r="AI192">
+        <v>0.44615384615384601</v>
+      </c>
+      <c r="AJ192">
+        <v>4.7755030347459296E-3</v>
+      </c>
+      <c r="AK192">
+        <v>6.51204959283537E-3</v>
+      </c>
+      <c r="AL192">
+        <v>0</v>
+      </c>
+      <c r="AM192">
+        <v>0.59090909090909005</v>
+      </c>
+    </row>
+    <row r="193" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>23</v>
+      </c>
+      <c r="B193" t="s">
+        <v>48</v>
+      </c>
+      <c r="C193" t="s">
+        <v>69</v>
+      </c>
+      <c r="D193">
+        <v>2027</v>
+      </c>
+      <c r="E193">
+        <v>7</v>
+      </c>
+      <c r="F193">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="G193">
+        <v>0.14285714285714199</v>
+      </c>
+      <c r="H193">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="I193">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="J193">
+        <v>1.8571428571428501</v>
+      </c>
+      <c r="K193">
+        <v>-1</v>
+      </c>
+      <c r="L193">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="M193">
+        <v>90</v>
+      </c>
+      <c r="N193">
+        <v>723.88621137688494</v>
+      </c>
+      <c r="O193">
+        <v>0.58395128829744003</v>
+      </c>
+      <c r="P193">
+        <v>0.33712984054669698</v>
+      </c>
+      <c r="Q193">
+        <v>0.86746031746031704</v>
+      </c>
+      <c r="R193">
+        <v>0.174206349206349</v>
+      </c>
+      <c r="S193">
+        <v>3.2781345049003E-2</v>
+      </c>
+      <c r="T193">
+        <v>0.247422680412371</v>
+      </c>
+      <c r="U193">
+        <v>0.31958762886597902</v>
+      </c>
+      <c r="V193">
+        <v>2.4332544778641399E-2</v>
+      </c>
+      <c r="W193">
+        <v>6.7252450152078397E-2</v>
+      </c>
+      <c r="X193">
+        <v>4.5961473470767102E-2</v>
+      </c>
+      <c r="Y193">
+        <v>0.53676470588235203</v>
+      </c>
+      <c r="Z193">
+        <v>3.41331530922609E-2</v>
+      </c>
+      <c r="AA193">
+        <v>3.3203626061756197E-2</v>
+      </c>
+      <c r="AB193">
+        <v>6.4984239578008599E-2</v>
+      </c>
+      <c r="AC193">
+        <v>0.72992700729926996</v>
+      </c>
+      <c r="AD193">
+        <v>2.2293863212893401E-2</v>
+      </c>
+      <c r="AE193">
+        <v>3.5575313637595897E-2</v>
+      </c>
+      <c r="AF193">
+        <v>7.3673538357553206E-2</v>
+      </c>
+      <c r="AG193">
+        <v>3.32036260617562E-3</v>
+      </c>
+      <c r="AH193">
+        <v>0.103405578306612</v>
+      </c>
+      <c r="AI193">
+        <v>0.45871559633027498</v>
+      </c>
+      <c r="AJ193">
+        <v>6.7762502166849401E-3</v>
+      </c>
+      <c r="AK193">
+        <v>9.48675030335892E-3</v>
+      </c>
+      <c r="AL193">
+        <v>9.4867503033589195E-4</v>
+      </c>
+      <c r="AM193">
+        <v>0.59375</v>
       </c>
     </row>
   </sheetData>
